--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7785" activeTab="3"/>
+    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -894,13 +894,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -950,6 +950,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -964,13 +971,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -983,46 +983,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1037,14 +999,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1067,7 +1036,54 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1081,32 +1097,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1176,7 +1176,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1188,121 +1194,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1320,7 +1212,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1338,25 +1356,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1407,20 +1407,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1440,17 +1444,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1472,169 +1479,162 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1643,7 +1643,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1658,10 +1658,10 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1670,7 +1670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1678,58 +1678,58 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1738,22 +1738,22 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>9</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>300.000000003492</v>
+        <v>279.99999996624</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4">
@@ -2521,14 +2521,14 @@
       </c>
       <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="38">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.136363636363636</v>
+        <v>0.204545454545455</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>17</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C17" s="43">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>28</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P9" s="8">
         <f t="shared" si="1"/>
-        <v>480.000000003492</v>
+        <v>479.999999951106</v>
       </c>
       <c r="Q9" s="30" t="s">
         <v>21</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="P10" s="8">
         <f t="shared" si="1"/>
-        <v>120.000000003492</v>
+        <v>119.999999951106</v>
       </c>
       <c r="Q10" s="30" t="s">
         <v>21</v>
@@ -3306,7 +3306,7 @@
         <v/>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R11" s="28" t="str">
         <f t="shared" si="2"/>
@@ -3355,18 +3355,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="8" t="str">
+      <c r="N12" s="24">
+        <v>46121.5833333333</v>
+      </c>
+      <c r="O12" s="24">
+        <v>46121.75</v>
+      </c>
+      <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>239.999999996508</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R12" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R12" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46123</v>
       </c>
       <c r="S12" s="27" t="s">
         <v>82</v>
@@ -3418,7 +3422,7 @@
         <v/>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R13" s="28" t="str">
         <f t="shared" si="2"/>
@@ -5548,7 +5552,7 @@
         <v>91</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>82</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" ht="30" spans="1:7">
@@ -5571,7 +5575,7 @@
         <v>91</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>82</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:7">
@@ -6354,10 +6358,12 @@
       <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5" t="str">
+      <c r="A8" s="4">
+        <v>46119</v>
+      </c>
+      <c r="B8" s="5">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7"/>
@@ -6372,10 +6378,12 @@
       <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="str">
+      <c r="A9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B9" s="5">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7"/>
@@ -6390,10 +6398,12 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="str">
+      <c r="A10" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B10" s="5">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -894,11 +894,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
@@ -969,15 +969,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -998,8 +1004,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1007,6 +1014,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1020,15 +1034,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1059,7 +1067,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1067,7 +1082,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1092,21 +1107,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1176,7 +1176,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1188,79 +1344,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1273,90 +1357,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1390,41 +1390,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1447,6 +1417,45 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -1455,9 +1464,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1476,27 +1487,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1505,133 +1505,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>9</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>279.99999996624</v>
+        <v>743.999999990221</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>13</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.204545454545455</v>
+        <v>0.25</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>17</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C17" s="43">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>28</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v>239.999999996508</v>
+        <v>240.000000048894</v>
       </c>
       <c r="Q12" s="30" t="s">
         <v>21</v>
@@ -3471,18 +3471,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="8" t="str">
+      <c r="N14" s="24">
+        <v>46123</v>
+      </c>
+      <c r="O14" s="24">
+        <v>46123</v>
+      </c>
+      <c r="P14" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R14" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R14" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46125</v>
       </c>
       <c r="S14" s="27" t="s">
         <v>82</v>
@@ -3527,18 +3531,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="8" t="str">
+      <c r="N15" s="24">
+        <v>46124</v>
+      </c>
+      <c r="O15" s="24">
+        <v>46126</v>
+      </c>
+      <c r="P15" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2880</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R15" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R15" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46128</v>
       </c>
       <c r="S15" s="27" t="s">
         <v>82</v>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F20F53E3-C4F7-4662-83C5-4CB04B4B3422}"/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
+    <workbookView xWindow="2205" yWindow="3075" windowWidth="21885" windowHeight="12255" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -13,39 +19,52 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -56,20 +75,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -892,17 +911,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="178" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,202 +929,58 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1118,8 +989,14 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,194 +1051,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1389,427 +1080,173 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1861,53 +1298,21 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1921,9 +1326,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1962,9 +1373,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3"/>
+        <xdr:cNvPr id="2" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2008,9 +1425,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3"/>
+        <xdr:cNvPr id="3" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2045,7 +1468,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2059,9 +1482,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2100,9 +1529,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2"/>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2146,9 +1581,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2"/>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2183,66 +1624,78 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Suggested Seq"/>
-    <tableColumn id="3" name="Type"/>
-    <tableColumn id="4" name="Chapter Part"/>
-    <tableColumn id="5" name="Topic / Task"/>
-    <tableColumn id="6" name="Goal" dataDxfId="0"/>
-    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
-    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
-    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
-    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
-    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
-    <tableColumn id="12" name="Read End" dataDxfId="6"/>
-    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
-    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
-    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
-    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
-    <tableColumn id="17" name="Status" dataDxfId="11"/>
-    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
-    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
-    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
-    <tableColumn id="21" name="Notes" dataDxfId="15"/>
-    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
+      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
+      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
+      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
+      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Exercises"/>
-    <tableColumn id="3" name="Topic Cluster"/>
-    <tableColumn id="4" name="Why this set matters"/>
-    <tableColumn id="5" name="Priority"/>
-    <tableColumn id="6" name="Suggested after"/>
-    <tableColumn id="7" name="Done?"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Date"/>
-    <tableColumn id="2" name="Day #"/>
-    <tableColumn id="3" name="Units touched"/>
-    <tableColumn id="4" name="Read min"/>
-    <tableColumn id="5" name="Ex min"/>
-    <tableColumn id="6" name="Actual total min"/>
-    <tableColumn id="7" name="Big takeaway"/>
-    <tableColumn id="8" name="Blocker"/>
-    <tableColumn id="9" name="Next action"/>
-    <tableColumn id="10" name="Mood / energy"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
+      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
+      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2418,227 +1871,233 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:4">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:4">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="34">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="34">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:4">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
         <v>11</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="38" t="str">
+      <c r="D6" s="34" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:4">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>743.999999990221</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:4">
-      <c r="A8" s="36" t="s">
+        <v>743.99999999022111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
         <v>5</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="34">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:4">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="str">
+      <c r="D9" s="33" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:4">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
         <v>0.25</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="37" t="str">
+      <c r="D10" s="33" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:4">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:4">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:1">
-      <c r="A13" s="41" t="s">
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:4">
-      <c r="A15" s="42" t="s">
+    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>4</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4">
-      <c r="A17" s="42" t="s">
+    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="38">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>7</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="39" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2647,16 +2106,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2668,10 +2126,17 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2679,7 +2144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" spans="10:11">
+    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2687,17 +2152,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="31">
         <v>46114</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2707,7 +2172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="21.95" customHeight="1" spans="4:11">
+    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2718,10 +2183,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
         <v>40</v>
       </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2729,91 +2201,160 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A7" s="35" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A8" s="35" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A9" s="35" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A10" s="35" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+    </row>
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A11" s="35" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1"/>
-    <row r="13" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A13" s="34" t="s">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+    </row>
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A14" s="35" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+    </row>
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A15" s="35" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A16" s="35" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+    </row>
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
         <v>52</v>
       </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2829,2628 +2370,2662 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" ht="15.75"/>
-    <row r="4" ht="24" customHeight="1" spans="1:22">
-      <c r="A4" s="15" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:22">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="17">
         <v>60</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="8" t="str">
+      <c r="J5" s="17"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="6" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="8" t="str">
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="6" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="28" t="str">
+      <c r="R5" s="26" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" s="27"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:22">
-      <c r="A6" s="17" t="s">
+      <c r="S5" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="25"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+    </row>
+    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <v>2</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <v>60</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="8" t="str">
+      <c r="J6" s="17"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="Q6" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="28" t="str">
+      <c r="R6" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="27"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:22">
-      <c r="A7" s="17" t="s">
+      <c r="S6" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T6" s="25"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+    </row>
+    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <v>3</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <v>3</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <v>75</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="8" t="str">
+      <c r="J7" s="17"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="28" t="str">
+      <c r="R7" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:22">
-      <c r="A8" s="17" t="s">
+      <c r="S7" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T7" s="25"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+    </row>
+    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <v>4</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <v>75</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="8" t="str">
+      <c r="J8" s="17"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="27" t="s">
+      <c r="Q8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="28" t="str">
+      <c r="R8" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T8" s="27"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:22">
-      <c r="A9" s="17" t="s">
+      <c r="S8" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="25"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+    </row>
+    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <v>5</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17">
         <v>60</v>
       </c>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N9" s="24">
-        <v>46118.4166666667</v>
-      </c>
-      <c r="O9" s="24">
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <v>46118.416666666701</v>
+      </c>
+      <c r="O9" s="22">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="6">
         <f t="shared" si="1"/>
-        <v>479.999999951106</v>
-      </c>
-      <c r="Q9" s="30" t="s">
+        <v>479.99999995110556</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:22">
-      <c r="A10" s="17" t="s">
+      <c r="S9" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T9" s="28"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+    </row>
+    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>6</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="17">
         <v>6</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17">
         <v>60</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N10" s="24">
-        <v>46119.5416666667</v>
-      </c>
-      <c r="O10" s="24">
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N10" s="22">
+        <v>46119.541666666701</v>
+      </c>
+      <c r="O10" s="22">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="6">
         <f t="shared" si="1"/>
-        <v>119.999999951106</v>
-      </c>
-      <c r="Q10" s="30" t="s">
+        <v>119.99999995110556</v>
+      </c>
+      <c r="Q10" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="26">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:22">
-      <c r="A11" s="17" t="s">
+      <c r="S10" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T10" s="28"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+    </row>
+    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <v>7</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="17">
         <v>7</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17">
         <v>50</v>
       </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="8" t="str">
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="Q11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="28" t="str">
+      <c r="R11" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T11" s="30"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:22">
-      <c r="A12" s="17" t="s">
+      <c r="S11" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+    </row>
+    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="17">
         <v>8</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17">
         <v>50</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <v>46121.5833333333</v>
-      </c>
-      <c r="O12" s="24">
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <v>46121.583333333299</v>
+      </c>
+      <c r="O12" s="22">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="6">
         <f t="shared" si="1"/>
-        <v>240.000000048894</v>
-      </c>
-      <c r="Q12" s="30" t="s">
+        <v>240.00000004889444</v>
+      </c>
+      <c r="Q12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="26">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:22">
-      <c r="A13" s="17" t="s">
+      <c r="S12" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" s="28"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+    </row>
+    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <v>9</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="17">
         <v>9</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17">
         <v>50</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="8" t="str">
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="Q13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="28" t="str">
+      <c r="R13" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T13" s="30"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:22">
-      <c r="A14" s="17" t="s">
+      <c r="S13" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="28"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+    </row>
+    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="17">
         <v>10</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19">
+      <c r="I14" s="17"/>
+      <c r="J14" s="17">
         <v>60</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N14" s="24">
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N14" s="22">
         <v>46123</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="22">
         <v>46123</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="30" t="s">
+      <c r="Q14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="28">
+      <c r="R14" s="26">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:22">
-      <c r="A15" s="17" t="s">
+      <c r="S14" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+    </row>
+    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <v>11</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="17">
         <v>11</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19">
+      <c r="I15" s="17"/>
+      <c r="J15" s="17">
         <v>60</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N15" s="24">
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N15" s="22">
         <v>46124</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="22">
         <v>46126</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="6">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="30" t="s">
+      <c r="Q15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="26">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T15" s="30"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:22">
-      <c r="A16" s="21" t="s">
+      <c r="S15" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T15" s="28"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+    </row>
+    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>12</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="21">
         <v>12</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="21">
         <v>45</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="26" t="str">
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="24" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R16" s="28" t="str">
+      <c r="R16" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T16" s="31"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:22">
-      <c r="A17" s="17" t="s">
+      <c r="S16" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T16" s="29"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+    </row>
+    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <v>13</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="17">
         <v>13</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="17">
         <v>50</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="8" t="str">
+      <c r="J17" s="17"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="27" t="s">
+      <c r="Q17" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R17" s="28" t="str">
+      <c r="R17" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T17" s="27"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:22">
-      <c r="A18" s="17" t="s">
+      <c r="S17" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T17" s="25"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+    </row>
+    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="15">
         <v>14</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="17">
         <v>14</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="17">
         <v>70</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="8" t="str">
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="27" t="s">
+      <c r="Q18" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R18" s="28" t="str">
+      <c r="R18" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T18" s="27"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:22">
-      <c r="A19" s="17" t="s">
+      <c r="S18" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T18" s="25"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+    </row>
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="15">
         <v>15</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="17">
         <v>15</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <v>80</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="8" t="str">
+      <c r="J19" s="17"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="Q19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R19" s="28" t="str">
+      <c r="R19" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T19" s="27"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:22">
-      <c r="A20" s="17" t="s">
+      <c r="S19" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T19" s="25"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+    </row>
+    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="15">
         <v>16</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="17">
         <v>16</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <v>60</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="8" t="str">
+      <c r="J20" s="17"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="27" t="s">
+      <c r="Q20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R20" s="28" t="str">
+      <c r="R20" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T20" s="27"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:22">
-      <c r="A21" s="17" t="s">
+      <c r="S20" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T20" s="25"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+    </row>
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <v>17</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="17">
         <v>17</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <v>80</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="8" t="str">
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q21" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R21" s="28" t="str">
+      <c r="R21" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T21" s="27"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:22">
-      <c r="A22" s="17" t="s">
+      <c r="S21" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T21" s="25"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+    </row>
+    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="15">
         <v>18</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="17">
         <v>18</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="17">
         <v>80</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="8" t="str">
+      <c r="J22" s="17"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="27" t="s">
+      <c r="Q22" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R22" s="28" t="str">
+      <c r="R22" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T22" s="27"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:22">
-      <c r="A23" s="17" t="s">
+      <c r="S22" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T22" s="25"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+    </row>
+    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="15">
         <v>19</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="17">
         <v>19</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17">
         <v>60</v>
       </c>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="8" t="str">
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q23" s="30" t="s">
+      <c r="Q23" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R23" s="28" t="str">
+      <c r="R23" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S23" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T23" s="30"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:22">
-      <c r="A24" s="17" t="s">
+      <c r="S23" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T23" s="28"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+    </row>
+    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <v>20</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="17">
         <v>20</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19">
+      <c r="I24" s="17"/>
+      <c r="J24" s="17">
         <v>60</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="8" t="str">
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q24" s="30" t="s">
+      <c r="Q24" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R24" s="28" t="str">
+      <c r="R24" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S24" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T24" s="30"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:22">
-      <c r="A25" s="17" t="s">
+      <c r="S24" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T24" s="28"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+    </row>
+    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <v>21</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="17">
         <v>21</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19">
+      <c r="I25" s="17"/>
+      <c r="J25" s="17">
         <v>60</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="8" t="str">
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q25" s="30" t="s">
+      <c r="Q25" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R25" s="28" t="str">
+      <c r="R25" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S25" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T25" s="30"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:22">
-      <c r="A26" s="17" t="s">
+      <c r="S25" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T25" s="28"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+    </row>
+    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="15">
         <v>22</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="17">
         <v>22</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19">
+      <c r="I26" s="17"/>
+      <c r="J26" s="17">
         <v>60</v>
       </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="8" t="str">
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q26" s="30" t="s">
+      <c r="Q26" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R26" s="28" t="str">
+      <c r="R26" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S26" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T26" s="30"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:22">
-      <c r="A27" s="17" t="s">
+      <c r="S26" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T26" s="28"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+    </row>
+    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="15">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="17">
         <v>23</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19">
+      <c r="I27" s="17"/>
+      <c r="J27" s="17">
         <v>60</v>
       </c>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="8" t="str">
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q27" s="30" t="s">
+      <c r="Q27" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R27" s="28" t="str">
+      <c r="R27" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S27" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T27" s="30"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:22">
-      <c r="A28" s="17" t="s">
+      <c r="S27" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T27" s="28"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+    </row>
+    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="15">
         <v>24</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="17">
         <v>24</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19">
+      <c r="I28" s="17"/>
+      <c r="J28" s="17">
         <v>70</v>
       </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="8" t="str">
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q28" s="30" t="s">
+      <c r="Q28" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R28" s="28" t="str">
+      <c r="R28" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S28" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T28" s="30"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:22">
-      <c r="A29" s="17" t="s">
+      <c r="S28" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T28" s="28"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+    </row>
+    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="15">
         <v>25</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="17">
         <v>25</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19">
+      <c r="I29" s="17"/>
+      <c r="J29" s="17">
         <v>70</v>
       </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="8" t="str">
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q29" s="30" t="s">
+      <c r="Q29" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R29" s="28" t="str">
+      <c r="R29" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S29" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T29" s="30"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:22">
-      <c r="A30" s="17" t="s">
+      <c r="S29" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T29" s="28"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+    </row>
+    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="15">
         <v>26</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="17">
         <v>26</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19">
+      <c r="I30" s="17"/>
+      <c r="J30" s="17">
         <v>70</v>
       </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="8" t="str">
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q30" s="30" t="s">
+      <c r="Q30" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R30" s="28" t="str">
+      <c r="R30" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S30" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T30" s="30"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:22">
-      <c r="A31" s="17" t="s">
+      <c r="S30" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T30" s="28"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+    </row>
+    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="15">
         <v>27</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="17">
         <v>27</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19">
+      <c r="I31" s="17"/>
+      <c r="J31" s="17">
         <v>70</v>
       </c>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="8" t="str">
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q31" s="30" t="s">
+      <c r="Q31" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R31" s="28" t="str">
+      <c r="R31" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S31" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T31" s="30"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:22">
-      <c r="A32" s="17" t="s">
+      <c r="S31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T31" s="28"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+    </row>
+    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="15">
         <v>28</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="17">
         <v>28</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19">
+      <c r="I32" s="17"/>
+      <c r="J32" s="17">
         <v>70</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="8" t="str">
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q32" s="30" t="s">
+      <c r="Q32" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R32" s="28" t="str">
+      <c r="R32" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S32" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T32" s="30"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:22">
-      <c r="A33" s="17" t="s">
+      <c r="S32" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T32" s="28"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+    </row>
+    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="15">
         <v>29</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="17">
         <v>29</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19">
+      <c r="I33" s="17"/>
+      <c r="J33" s="17">
         <v>70</v>
       </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="8" t="str">
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q33" s="30" t="s">
+      <c r="Q33" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R33" s="28" t="str">
+      <c r="R33" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S33" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T33" s="30"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:22">
-      <c r="A34" s="17" t="s">
+      <c r="S33" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T33" s="28"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="27"/>
+    </row>
+    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="15">
         <v>30</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="17">
         <v>30</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19">
+      <c r="I34" s="17"/>
+      <c r="J34" s="17">
         <v>70</v>
       </c>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="8" t="str">
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q34" s="30" t="s">
+      <c r="Q34" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R34" s="28" t="str">
+      <c r="R34" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S34" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T34" s="30"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:22">
-      <c r="A35" s="17" t="s">
+      <c r="S34" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T34" s="28"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="27"/>
+    </row>
+    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="15">
         <v>31</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="17">
         <v>31</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19">
+      <c r="I35" s="17"/>
+      <c r="J35" s="17">
         <v>70</v>
       </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="8" t="str">
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q35" s="30" t="s">
+      <c r="Q35" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R35" s="28" t="str">
+      <c r="R35" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S35" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T35" s="30"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:22">
-      <c r="A36" s="17" t="s">
+      <c r="S35" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T35" s="28"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+    </row>
+    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="15">
         <v>32</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="17">
         <v>32</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19">
+      <c r="I36" s="17"/>
+      <c r="J36" s="17">
         <v>70</v>
       </c>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="8" t="str">
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q36" s="30" t="s">
+      <c r="Q36" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R36" s="28" t="str">
+      <c r="R36" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S36" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T36" s="30"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:22">
-      <c r="A37" s="17" t="s">
+      <c r="S36" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T36" s="28"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="27"/>
+    </row>
+    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="15">
         <v>33</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="17">
         <v>33</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19">
+      <c r="I37" s="17"/>
+      <c r="J37" s="17">
         <v>70</v>
       </c>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="8" t="str">
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q37" s="30" t="s">
+      <c r="Q37" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R37" s="28" t="str">
+      <c r="R37" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S37" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T37" s="30"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:22">
-      <c r="A38" s="17" t="s">
+      <c r="S37" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T37" s="28"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+    </row>
+    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="15">
         <v>34</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="17">
         <v>34</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19">
+      <c r="I38" s="17"/>
+      <c r="J38" s="17">
         <v>70</v>
       </c>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="8" t="str">
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q38" s="30" t="s">
+      <c r="Q38" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R38" s="28" t="str">
+      <c r="R38" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S38" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T38" s="30"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:22">
-      <c r="A39" s="17" t="s">
+      <c r="S38" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T38" s="28"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="27"/>
+    </row>
+    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="15">
         <v>35</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="17">
         <v>35</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19">
+      <c r="I39" s="17"/>
+      <c r="J39" s="17">
         <v>70</v>
       </c>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="8" t="str">
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q39" s="30" t="s">
+      <c r="Q39" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R39" s="28" t="str">
+      <c r="R39" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S39" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T39" s="30"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:22">
-      <c r="A40" s="17" t="s">
+      <c r="S39" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T39" s="28"/>
+      <c r="U39" s="27"/>
+      <c r="V39" s="27"/>
+    </row>
+    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="15">
         <v>36</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="17">
         <v>36</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19">
+      <c r="I40" s="17"/>
+      <c r="J40" s="17">
         <v>80</v>
       </c>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="8" t="str">
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q40" s="30" t="s">
+      <c r="Q40" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R40" s="28" t="str">
+      <c r="R40" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S40" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T40" s="30"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:22">
-      <c r="A41" s="17" t="s">
+      <c r="S40" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T40" s="28"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+    </row>
+    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="15">
         <v>37</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="17">
         <v>37</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19">
+      <c r="I41" s="17"/>
+      <c r="J41" s="17">
         <v>80</v>
       </c>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="8" t="str">
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q41" s="30" t="s">
+      <c r="Q41" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R41" s="28" t="str">
+      <c r="R41" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S41" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T41" s="30"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:22">
-      <c r="A42" s="17" t="s">
+      <c r="S41" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T41" s="28"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+    </row>
+    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="15">
         <v>38</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="17">
         <v>38</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19">
+      <c r="I42" s="17"/>
+      <c r="J42" s="17">
         <v>80</v>
       </c>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="8" t="str">
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q42" s="30" t="s">
+      <c r="Q42" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R42" s="28" t="str">
+      <c r="R42" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S42" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T42" s="30"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:22">
-      <c r="A43" s="17" t="s">
+      <c r="S42" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T42" s="28"/>
+      <c r="U42" s="27"/>
+      <c r="V42" s="27"/>
+    </row>
+    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="15">
         <v>39</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="17">
         <v>39</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19">
+      <c r="I43" s="17"/>
+      <c r="J43" s="17">
         <v>80</v>
       </c>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="8" t="str">
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q43" s="30" t="s">
+      <c r="Q43" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R43" s="28" t="str">
+      <c r="R43" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S43" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T43" s="30"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="1:22">
-      <c r="A44" s="17" t="s">
+      <c r="S43" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T43" s="28"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+    </row>
+    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="15">
         <v>40</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="17">
         <v>40</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H44" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19">
+      <c r="I44" s="17"/>
+      <c r="J44" s="17">
         <v>80</v>
       </c>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="8" t="str">
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q44" s="30" t="s">
+      <c r="Q44" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R44" s="28" t="str">
+      <c r="R44" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S44" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T44" s="30"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:22">
-      <c r="A45" s="17" t="s">
+      <c r="S44" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T44" s="28"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="27"/>
+    </row>
+    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="15">
         <v>41</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="17">
         <v>41</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19">
+      <c r="I45" s="17"/>
+      <c r="J45" s="17">
         <v>80</v>
       </c>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="8" t="str">
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q45" s="30" t="s">
+      <c r="Q45" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R45" s="28" t="str">
+      <c r="R45" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S45" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T45" s="30"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:22">
-      <c r="A46" s="17" t="s">
+      <c r="S45" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T45" s="28"/>
+      <c r="U45" s="27"/>
+      <c r="V45" s="27"/>
+    </row>
+    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="15">
         <v>42</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="17">
         <v>42</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19">
+      <c r="I46" s="17"/>
+      <c r="J46" s="17">
         <v>70</v>
       </c>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="8" t="str">
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="30" t="s">
+      <c r="Q46" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="28" t="str">
+      <c r="R46" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T46" s="30"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" spans="1:22">
-      <c r="A47" s="17" t="s">
+      <c r="S46" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T46" s="28"/>
+      <c r="U46" s="27"/>
+      <c r="V46" s="27"/>
+    </row>
+    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="15">
         <v>43</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="17">
         <v>43</v>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19">
+      <c r="I47" s="17"/>
+      <c r="J47" s="17">
         <v>70</v>
       </c>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="8" t="str">
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="30" t="s">
+      <c r="Q47" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="28" t="str">
+      <c r="R47" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T47" s="30"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:22">
-      <c r="A48" s="21" t="s">
+      <c r="S47" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T47" s="28"/>
+      <c r="U47" s="27"/>
+      <c r="V47" s="27"/>
+    </row>
+    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="19">
         <v>44</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="21">
         <v>44</v>
       </c>
-      <c r="H48" s="20">
+      <c r="H48" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="21">
         <v>50</v>
       </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N48" s="25"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="26" t="str">
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N48" s="23"/>
+      <c r="O48" s="23"/>
+      <c r="P48" s="24" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="27" t="s">
+      <c r="Q48" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="28" t="str">
+      <c r="R48" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T48" s="31"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
+      <c r="S48" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T48" s="29"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
-      <formula1>Protocol!$J$1:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
-      <formula1>Protocol!$K$1:$K$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$J$1:$J$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q5:Q48</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$K$1:$K$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>T5:T48</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5461,772 +5036,778 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" ht="30" spans="1:7">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:7">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>12</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" ht="30" spans="1:7">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="1:7">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="1:7">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" ht="30" spans="1:7">
-      <c r="A9" s="9" t="s">
+      <c r="G8" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" ht="30" spans="1:7">
-      <c r="A10" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>25</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" ht="30" spans="1:7">
-      <c r="A11" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" ht="30" spans="1:7">
-      <c r="A12" s="9" t="s">
+      <c r="G11" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>4</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" ht="30" spans="1:7">
-      <c r="A13" s="9" t="s">
+      <c r="G12" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>5</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:7">
-      <c r="A14" s="9" t="s">
+      <c r="G13" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <v>6</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:7">
-      <c r="A15" s="9" t="s">
+      <c r="G14" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>8</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="9" t="s">
+      <c r="G15" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9" t="s">
+      <c r="G16" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <v>9</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9" t="s">
+      <c r="G17" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <v>10</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="1:7">
-      <c r="A19" s="9" t="s">
+      <c r="G18" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <v>15</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="1:7">
-      <c r="A20" s="9" t="s">
+      <c r="G19" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="7">
         <v>16</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" ht="30" spans="1:7">
-      <c r="A21" s="9" t="s">
+      <c r="G20" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" ht="30" spans="1:7">
-      <c r="A22" s="9" t="s">
+      <c r="G21" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" ht="30" spans="1:7">
-      <c r="A23" s="9" t="s">
+      <c r="G22" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>22</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="1:7">
-      <c r="A24" s="9" t="s">
+      <c r="G23" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>30</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:7">
-      <c r="A25" s="9" t="s">
+      <c r="G24" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="1:7">
-      <c r="A26" s="9" t="s">
+      <c r="G25" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <v>13</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" ht="30" spans="1:7">
-      <c r="A27" s="9" t="s">
+      <c r="G26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="7">
         <v>14</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" ht="30" spans="1:7">
-      <c r="A28" s="9" t="s">
+      <c r="G27" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" ht="30" spans="1:7">
-      <c r="A29" s="9" t="s">
+      <c r="G28" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" ht="30" spans="1:7">
-      <c r="A30" s="9" t="s">
+      <c r="G29" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" ht="30" spans="1:7">
-      <c r="A31" s="9" t="s">
+      <c r="G30" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>23</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" ht="30" spans="1:7">
-      <c r="A32" s="9" t="s">
+      <c r="G31" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="9" t="s">
+      <c r="G32" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="7">
         <v>33</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="9" t="s">
+      <c r="G33" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <v>31</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" ht="30" spans="1:7">
-      <c r="A35" s="9" t="s">
+      <c r="G34" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="7">
         <v>32</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="9" t="s">
         <v>82</v>
       </c>
     </row>
@@ -6234,13 +5815,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6248,10 +5829,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -6263,1147 +5843,1165 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46114</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="str">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46115</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46118</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46119</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46120</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>46121</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="str">
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="str">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="str">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5" t="str">
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="str">
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="str">
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="str">
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="str">
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="str">
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="str">
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="str">
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="str">
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="str">
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="str">
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="str">
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="str">
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="str">
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="str">
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5" t="str">
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="str">
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="str">
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="str">
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5" t="str">
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5" t="str">
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5" t="str">
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5" t="str">
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5" t="str">
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="8" t="str">
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5" t="str">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8" t="str">
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5" t="str">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8" t="str">
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5" t="str">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8" t="str">
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5" t="str">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8" t="str">
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5" t="str">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8" t="str">
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5" t="str">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8" t="str">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5" t="str">
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="8" t="str">
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5" t="str">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="8" t="str">
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5" t="str">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8" t="str">
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5" t="str">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="8" t="str">
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5" t="str">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="8" t="str">
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5" t="str">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="8" t="str">
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5" t="str">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8" t="str">
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5" t="str">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8" t="str">
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5" t="str">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8" t="str">
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5" t="str">
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8" t="str">
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5" t="str">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8" t="str">
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5" t="str">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="8" t="str">
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="str">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8" t="str">
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5" t="str">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8" t="str">
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5" t="str">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8" t="str">
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5" t="str">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8" t="str">
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5" t="str">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8" t="str">
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5" t="str">
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8" t="str">
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5" t="str">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="8" t="str">
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="str">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="8" t="str">
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5" t="str">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8" t="str">
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F20F53E3-C4F7-4662-83C5-4CB04B4B3422}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A05CAB-D096-4462-BEED-451A2F25D36A}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="3075" windowWidth="21885" windowHeight="12255" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -913,9 +913,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1090,7 +1090,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1134,7 +1134,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1146,10 +1146,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1158,7 +1158,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1171,7 +1171,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1181,7 +1181,7 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -1202,10 +1202,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -1623,6 +1623,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
   <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -1920,7 +1924,7 @@
       </c>
       <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>9</v>
@@ -1968,7 +1972,7 @@
       </c>
       <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>743.99999999022111</v>
+        <v>531.42857142158653</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1977,7 +1981,7 @@
       </c>
       <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>13</v>
@@ -2009,7 +2013,7 @@
       </c>
       <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.25</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>17</v>
@@ -2063,7 +2067,7 @@
       </c>
       <c r="C15" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>24</v>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="C16" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>26</v>
@@ -2095,7 +2099,7 @@
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>28</v>
@@ -2184,7 +2188,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="45" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="41"/>
@@ -2202,7 +2206,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>43</v>
       </c>
       <c r="B6" s="41"/>
@@ -2214,7 +2218,7 @@
       <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="44" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="41"/>
@@ -2226,7 +2230,7 @@
       <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="44" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="41"/>
@@ -2238,7 +2242,7 @@
       <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="41"/>
@@ -2250,7 +2254,7 @@
       <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="44" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="41"/>
@@ -2262,7 +2266,7 @@
       <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="41"/>
@@ -2275,7 +2279,7 @@
     </row>
     <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="45" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="41"/>
@@ -2287,7 +2291,7 @@
       <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="44" t="s">
         <v>50</v>
       </c>
       <c r="B14" s="41"/>
@@ -2299,7 +2303,7 @@
       <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="44" t="s">
         <v>51</v>
       </c>
       <c r="B15" s="41"/>
@@ -2311,7 +2315,7 @@
       <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="44" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="41"/>
@@ -2324,6 +2328,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A9:H9"/>
@@ -2331,11 +2340,6 @@
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3162,7 +3166,7 @@
         <v/>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R16" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3218,7 +3222,7 @@
         <v/>
       </c>
       <c r="Q17" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R17" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3274,7 +3278,7 @@
         <v/>
       </c>
       <c r="Q18" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R18" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3330,7 +3334,7 @@
         <v/>
       </c>
       <c r="Q19" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R19" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3386,7 +3390,7 @@
         <v/>
       </c>
       <c r="Q20" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R20" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3442,7 +3446,7 @@
         <v/>
       </c>
       <c r="Q21" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R21" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3498,7 +3502,7 @@
         <v/>
       </c>
       <c r="Q22" s="25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R22" s="26" t="str">
         <f t="shared" si="2"/>
@@ -3547,18 +3551,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="6" t="str">
+      <c r="N23" s="22">
+        <v>46143</v>
+      </c>
+      <c r="O23" s="22">
+        <v>46143</v>
+      </c>
+      <c r="P23" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q23" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R23" s="26" t="str">
+        <v>21</v>
+      </c>
+      <c r="R23" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46145</v>
       </c>
       <c r="S23" s="25" t="s">
         <v>82</v>
@@ -3603,18 +3611,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="6" t="str">
+      <c r="N24" s="22">
+        <v>46144</v>
+      </c>
+      <c r="O24" s="22">
+        <v>46144</v>
+      </c>
+      <c r="P24" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q24" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R24" s="26" t="str">
+        <v>21</v>
+      </c>
+      <c r="R24" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="S24" s="25" t="s">
         <v>82</v>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A05CAB-D096-4462-BEED-451A2F25D36A}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FA26B89-5CB0-4524-B8A7-5EE9E51D729E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>9</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>531.42857142158653</v>
+        <v>573.33333332790062</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>13</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.45454545454545453</v>
+        <v>0.47727272727272729</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>17</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>28</v>
@@ -3671,18 +3671,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="6" t="str">
+      <c r="N25" s="22">
+        <v>46145</v>
+      </c>
+      <c r="O25" s="22">
+        <v>46145</v>
+      </c>
+      <c r="P25" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q25" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R25" s="26" t="str">
+        <v>21</v>
+      </c>
+      <c r="R25" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46147</v>
       </c>
       <c r="S25" s="25" t="s">
         <v>82</v>
@@ -3727,18 +3731,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="6" t="str">
+      <c r="N26" s="22">
+        <v>46147</v>
+      </c>
+      <c r="O26" s="22">
+        <v>46148</v>
+      </c>
+      <c r="P26" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1440</v>
       </c>
       <c r="Q26" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R26" s="26" t="str">
+      <c r="R26" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46150</v>
       </c>
       <c r="S26" s="25" t="s">
         <v>82</v>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_01F34EFC9B3AEB9EA895230763713F60C8048F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FA26B89-5CB0-4524-B8A7-5EE9E51D729E}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_1327E116937BED0EA895230763713F4036575F06" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27086029-37F6-40A9-8D48-10F564391581}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -914,8 +914,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1146,13 +1146,13 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1181,7 +1181,7 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -1202,10 +1202,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -1623,10 +1623,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
   <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -1924,7 +1920,7 @@
       </c>
       <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1945,7 @@
       </c>
       <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>9</v>
@@ -1972,7 +1968,7 @@
       </c>
       <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>573.33333332790062</v>
+        <v>338.18181817737326</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1981,7 +1977,7 @@
       </c>
       <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>13</v>
@@ -2013,7 +2009,7 @@
       </c>
       <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.47727272727272729</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>17</v>
@@ -2099,7 +2095,7 @@
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>28</v>
@@ -2188,7 +2184,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="44" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="41"/>
@@ -2206,7 +2202,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="45" t="s">
         <v>43</v>
       </c>
       <c r="B6" s="41"/>
@@ -2218,7 +2214,7 @@
       <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="45" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="41"/>
@@ -2230,7 +2226,7 @@
       <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="45" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="41"/>
@@ -2242,7 +2238,7 @@
       <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="45" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="41"/>
@@ -2254,7 +2250,7 @@
       <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="45" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="41"/>
@@ -2266,7 +2262,7 @@
       <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="45" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="41"/>
@@ -2279,7 +2275,7 @@
     </row>
     <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="44" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="41"/>
@@ -2291,7 +2287,7 @@
       <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="45" t="s">
         <v>50</v>
       </c>
       <c r="B14" s="41"/>
@@ -2303,7 +2299,7 @@
       <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="45" t="s">
         <v>51</v>
       </c>
       <c r="B15" s="41"/>
@@ -2315,7 +2311,7 @@
       <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="45" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="41"/>
@@ -2328,11 +2324,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A9:H9"/>
@@ -2340,6 +2331,11 @@
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3161,7 +3157,7 @@
       </c>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
-      <c r="P16" s="24" t="str">
+      <c r="P16" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3735,18 +3731,18 @@
         <v>46147</v>
       </c>
       <c r="O26" s="22">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="1"/>
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="28" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R26" s="26">
         <f t="shared" si="2"/>
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="S26" s="25" t="s">
         <v>82</v>
@@ -3791,18 +3787,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="6" t="str">
+      <c r="N27" s="22">
+        <v>46148</v>
+      </c>
+      <c r="O27" s="22">
+        <v>46148</v>
+      </c>
+      <c r="P27" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q27" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R27" s="26" t="str">
+        <v>21</v>
+      </c>
+      <c r="R27" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46150</v>
       </c>
       <c r="S27" s="25" t="s">
         <v>82</v>
@@ -3847,18 +3847,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="6" t="str">
+      <c r="N28" s="22">
+        <v>46149</v>
+      </c>
+      <c r="O28" s="22">
+        <v>46149</v>
+      </c>
+      <c r="P28" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q28" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R28" s="26" t="str">
+        <v>21</v>
+      </c>
+      <c r="R28" s="26">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46151</v>
       </c>
       <c r="S28" s="25" t="s">
         <v>82</v>
@@ -4967,9 +4971,9 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="24" t="str">
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1327E116937BED0EA895230763713F4036575F06" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27086029-37F6-40A9-8D48-10F564391581}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,52 +13,39 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -75,20 +56,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -911,13 +892,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,58 +914,202 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -989,14 +1118,8 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1051,8 +1174,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1080,173 +1389,427 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1298,21 +1861,53 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1326,15 +1921,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1373,15 +1962,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1425,15 +2008,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1468,7 +2045,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1482,15 +2059,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1529,15 +2100,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1581,15 +2146,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1624,78 +2183,66 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
-      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
-      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
-      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
-      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Suggested Seq"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Chapter Part"/>
+    <tableColumn id="5" name="Topic / Task"/>
+    <tableColumn id="6" name="Goal" dataDxfId="0"/>
+    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
+    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
+    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
+    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
+    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
+    <tableColumn id="12" name="Read End" dataDxfId="6"/>
+    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
+    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
+    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
+    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
+    <tableColumn id="17" name="Status" dataDxfId="11"/>
+    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
+    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
+    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
+    <tableColumn id="21" name="Notes" dataDxfId="15"/>
+    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Exercises"/>
+    <tableColumn id="3" name="Topic Cluster"/>
+    <tableColumn id="4" name="Why this set matters"/>
+    <tableColumn id="5" name="Priority"/>
+    <tableColumn id="6" name="Suggested after"/>
+    <tableColumn id="7" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
-      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
-      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Day #"/>
+    <tableColumn id="3" name="Units touched"/>
+    <tableColumn id="4" name="Read min"/>
+    <tableColumn id="5" name="Ex min"/>
+    <tableColumn id="6" name="Actual total min"/>
+    <tableColumn id="7" name="Big takeaway"/>
+    <tableColumn id="8" name="Blocker"/>
+    <tableColumn id="9" name="Next action"/>
+    <tableColumn id="10" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1871,233 +2418,227 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1" spans="1:4">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" ht="24" customHeight="1" spans="1:4">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:4">
+      <c r="A5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="38">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="38">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+    <row r="6" ht="24" customHeight="1" spans="1:4">
+      <c r="A6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>24</v>
-      </c>
-      <c r="C6" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="34" t="str">
+      <c r="D6" s="38" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:4">
+      <c r="A7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>338.18181817737326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+        <v>286.153846150085</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:4">
+      <c r="A8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>11</v>
-      </c>
-      <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="34">
+      <c r="C8" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="38">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+    <row r="9" ht="24" customHeight="1" spans="1:4">
+      <c r="A9" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="33" t="str">
+      <c r="D9" s="37" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" ht="24" customHeight="1" spans="1:4">
+      <c r="A10" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="C10" s="32" t="s">
+        <v>0.590909090909091</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="33" t="str">
+      <c r="D10" s="37" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:4">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:4">
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:1">
+      <c r="A13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:4">
+      <c r="A15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+    <row r="16" ht="24" customHeight="1" spans="1:4">
+      <c r="A16" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="44" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:4">
+      <c r="A17" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="43">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="43">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>13</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="44" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2106,15 +2647,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2126,17 +2668,10 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2144,7 +2679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="21.95" customHeight="1" spans="10:11">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2152,17 +2687,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A3" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="33">
         <v>46114</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2172,7 +2707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="21.95" customHeight="1" spans="4:11">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2183,17 +2718,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+    <row r="5" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2201,160 +2729,91 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+    <row r="6" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+    </row>
+    <row r="7" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A7" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-    </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A8" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-    </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+    </row>
+    <row r="9" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-    </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+    </row>
+    <row r="10" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A10" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-    </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+    </row>
+    <row r="11" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A11" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-    </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+    </row>
+    <row r="12" ht="21.95" customHeight="1"/>
+    <row r="13" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A13" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-    </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+    </row>
+    <row r="14" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-    </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+    </row>
+    <row r="15" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A15" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-    </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+    </row>
+    <row r="16" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A16" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="10" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2370,2686 +2829,2660 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="15.75"/>
+    <row r="4" ht="24" customHeight="1" spans="1:22">
+      <c r="A4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="24" customHeight="1" spans="1:22">
+      <c r="A5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <v>1</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="19">
         <v>60</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="6" t="str">
+      <c r="J5" s="19"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="8" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="6" t="str">
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="8" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="26" t="str">
+      <c r="R5" s="28" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="25"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-    </row>
-    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="T5" s="27"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:22">
+      <c r="A6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="19">
         <v>2</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="19">
         <v>60</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="6" t="str">
+      <c r="J6" s="19"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="6" t="str">
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="26" t="str">
+      <c r="R6" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="S6" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T6" s="25"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-    </row>
-    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="T6" s="27"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:22">
+      <c r="A7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="19">
         <v>3</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="19">
         <v>75</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="6" t="str">
+      <c r="J7" s="19"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="6" t="str">
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="26" t="str">
+      <c r="R7" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T7" s="25"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-    </row>
-    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="T7" s="27"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:22">
+      <c r="A8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="19">
         <v>4</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="19">
         <v>75</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="6" t="str">
+      <c r="J8" s="19"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="6" t="str">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="Q8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="26" t="str">
+      <c r="R8" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="25" t="s">
+      <c r="S8" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="25"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-    </row>
-    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="T8" s="27"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:22">
+      <c r="A9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="17">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="19">
         <v>5</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17">
+      <c r="I9" s="19"/>
+      <c r="J9" s="19">
         <v>60</v>
       </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="6" t="str">
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N9" s="22">
-        <v>46118.416666666701</v>
-      </c>
-      <c r="O9" s="22">
+      <c r="N9" s="24">
+        <v>46118.4166666667</v>
+      </c>
+      <c r="O9" s="24">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="8">
         <f t="shared" si="1"/>
-        <v>479.99999995110556</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+        <v>479.999999951106</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="28">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="25" t="s">
+      <c r="S9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T9" s="28"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-    </row>
-    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="T9" s="30"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:22">
+      <c r="A10" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="17">
         <v>6</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="19">
         <v>6</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17">
+      <c r="I10" s="19"/>
+      <c r="J10" s="19">
         <v>60</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="6" t="str">
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N10" s="22">
-        <v>46119.541666666701</v>
-      </c>
-      <c r="O10" s="22">
+      <c r="N10" s="24">
+        <v>46119.5416666667</v>
+      </c>
+      <c r="O10" s="24">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="8">
         <f t="shared" si="1"/>
-        <v>119.99999995110556</v>
-      </c>
-      <c r="Q10" s="28" t="s">
+        <v>119.999999951106</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="28">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="25" t="s">
+      <c r="S10" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T10" s="28"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-    </row>
-    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="T10" s="30"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:22">
+      <c r="A11" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="17">
         <v>7</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="19">
         <v>7</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17">
+      <c r="I11" s="19"/>
+      <c r="J11" s="19">
         <v>50</v>
       </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="6" t="str">
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="6" t="str">
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="28" t="s">
+      <c r="Q11" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="26" t="str">
+      <c r="R11" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="25" t="s">
+      <c r="S11" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-    </row>
-    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="T11" s="30"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:22">
+      <c r="A12" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="17">
         <v>8</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <v>8</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17">
+      <c r="I12" s="19"/>
+      <c r="J12" s="19">
         <v>50</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="6" t="str">
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N12" s="22">
-        <v>46121.583333333299</v>
-      </c>
-      <c r="O12" s="22">
+      <c r="N12" s="24">
+        <v>46121.5833333333</v>
+      </c>
+      <c r="O12" s="24">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v>240.00000004889444</v>
-      </c>
-      <c r="Q12" s="28" t="s">
+        <v>240.000000048894</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="28">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="25" t="s">
+      <c r="S12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T12" s="28"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-    </row>
-    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="T12" s="30"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:22">
+      <c r="A13" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="17">
         <v>9</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <v>9</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17">
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
         <v>50</v>
       </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="6" t="str">
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="6" t="str">
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="28" t="s">
+      <c r="Q13" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="26" t="str">
+      <c r="R13" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="25" t="s">
+      <c r="S13" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T13" s="28"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-    </row>
-    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="T13" s="30"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:22">
+      <c r="A14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="17">
         <v>10</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="19">
         <v>10</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17">
+      <c r="I14" s="19"/>
+      <c r="J14" s="19">
         <v>60</v>
       </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="6" t="str">
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="24">
         <v>46123</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="24">
         <v>46123</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="28" t="s">
+      <c r="Q14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="28">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="25" t="s">
+      <c r="S14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-    </row>
-    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="T14" s="30"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:22">
+      <c r="A15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="17">
         <v>11</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <v>11</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17">
+      <c r="I15" s="19"/>
+      <c r="J15" s="19">
         <v>60</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="6" t="str">
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="24">
         <v>46124</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="24">
         <v>46126</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="8">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="28" t="s">
+      <c r="Q15" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="28">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="25" t="s">
+      <c r="S15" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-    </row>
-    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="T15" s="30"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:22">
+      <c r="A16" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
         <v>12</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="23">
         <v>12</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="23">
         <v>45</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="6" t="str">
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="23" t="str">
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="26" t="str">
+      <c r="R16" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="29" t="s">
+      <c r="S16" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T16" s="29"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-    </row>
-    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:22">
+      <c r="A17" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="17">
         <v>13</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="19">
         <v>13</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="19">
         <v>50</v>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="6" t="str">
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="6" t="str">
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="26" t="str">
+      <c r="R17" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="S17" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T17" s="25"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-    </row>
-    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="T17" s="27"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:22">
+      <c r="A18" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <v>14</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="19">
         <v>14</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="19">
         <v>70</v>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="6" t="str">
+      <c r="J18" s="19"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="6" t="str">
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="25" t="s">
+      <c r="Q18" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="26" t="str">
+      <c r="R18" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="25" t="s">
+      <c r="S18" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T18" s="25"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-    </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="T18" s="27"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:22">
+      <c r="A19" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="17">
         <v>15</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="19">
         <v>15</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="19">
         <v>80</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="6" t="str">
+      <c r="J19" s="19"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="6" t="str">
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="25" t="s">
+      <c r="Q19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="26" t="str">
+      <c r="R19" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="25" t="s">
+      <c r="S19" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T19" s="25"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-    </row>
-    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="T19" s="27"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:22">
+      <c r="A20" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="17">
         <v>16</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="19">
         <v>16</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="19">
         <v>60</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="6" t="str">
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="6" t="str">
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="26" t="str">
+      <c r="R20" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="25" t="s">
+      <c r="S20" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T20" s="25"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-    </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="T20" s="27"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:22">
+      <c r="A21" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="17">
         <v>17</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="19">
         <v>17</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="19">
         <v>80</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="6" t="str">
+      <c r="J21" s="19"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="6" t="str">
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="25" t="s">
+      <c r="Q21" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="26" t="str">
+      <c r="R21" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="25" t="s">
+      <c r="S21" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T21" s="25"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-    </row>
-    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="T21" s="27"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:22">
+      <c r="A22" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="17">
         <v>18</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="19">
         <v>18</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="19">
         <v>80</v>
       </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="6" t="str">
+      <c r="J22" s="19"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="6" t="str">
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="25" t="s">
+      <c r="Q22" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="26" t="str">
+      <c r="R22" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="25" t="s">
+      <c r="S22" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-    </row>
-    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="T22" s="27"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:22">
+      <c r="A23" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="17">
         <v>19</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="19">
         <v>19</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19">
         <v>60</v>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="6" t="str">
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="24">
         <v>46143</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="24">
         <v>46143</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="28" t="s">
+      <c r="Q23" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="28">
         <f t="shared" si="2"/>
         <v>46145</v>
       </c>
-      <c r="S23" s="25" t="s">
+      <c r="S23" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T23" s="28"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-    </row>
-    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="T23" s="30"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:22">
+      <c r="A24" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="17">
         <v>20</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="19">
         <v>20</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19">
         <v>60</v>
       </c>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="6" t="str">
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="24">
         <v>46144</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="24">
         <v>46144</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="28" t="s">
+      <c r="Q24" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="28">
         <f t="shared" si="2"/>
         <v>46146</v>
       </c>
-      <c r="S24" s="25" t="s">
+      <c r="S24" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T24" s="28"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-    </row>
-    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="T24" s="30"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:22">
+      <c r="A25" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="17">
         <v>21</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <v>21</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17">
+      <c r="I25" s="19"/>
+      <c r="J25" s="19">
         <v>60</v>
       </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="6" t="str">
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="24">
         <v>46145</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="24">
         <v>46145</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="28" t="s">
+      <c r="Q25" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="28">
         <f t="shared" si="2"/>
         <v>46147</v>
       </c>
-      <c r="S25" s="25" t="s">
+      <c r="S25" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T25" s="28"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-    </row>
-    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="T25" s="30"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:22">
+      <c r="A26" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <v>22</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="19">
         <v>22</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17">
+      <c r="I26" s="19"/>
+      <c r="J26" s="19">
         <v>60</v>
       </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="6" t="str">
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="24">
         <v>46147</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="24">
         <v>46147</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="28" t="s">
+      <c r="Q26" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="28">
         <f t="shared" si="2"/>
         <v>46149</v>
       </c>
-      <c r="S26" s="25" t="s">
+      <c r="S26" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T26" s="28"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-    </row>
-    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="T26" s="30"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:22">
+      <c r="A27" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="17">
         <v>23</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="19">
         <v>23</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17">
+      <c r="I27" s="19"/>
+      <c r="J27" s="19">
         <v>60</v>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="6" t="str">
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="24">
         <v>46148</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="24">
         <v>46148</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="28" t="s">
+      <c r="Q27" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="28">
         <f t="shared" si="2"/>
         <v>46150</v>
       </c>
-      <c r="S27" s="25" t="s">
+      <c r="S27" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T27" s="28"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-    </row>
-    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="T27" s="30"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:22">
+      <c r="A28" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="17">
         <v>24</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="19">
         <v>24</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17">
+      <c r="I28" s="19"/>
+      <c r="J28" s="19">
         <v>70</v>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="6" t="str">
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="24">
         <v>46149</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="24">
         <v>46149</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="28" t="s">
+      <c r="Q28" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="28">
         <f t="shared" si="2"/>
         <v>46151</v>
       </c>
-      <c r="S28" s="25" t="s">
+      <c r="S28" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T28" s="28"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-    </row>
-    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="T28" s="30"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:22">
+      <c r="A29" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="17">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="19">
         <v>25</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17">
+      <c r="I29" s="19"/>
+      <c r="J29" s="19">
         <v>70</v>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="6" t="str">
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="6" t="str">
+      <c r="N29" s="24">
+        <v>46150</v>
+      </c>
+      <c r="O29" s="24">
+        <v>46150</v>
+      </c>
+      <c r="P29" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q29" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R29" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S29" s="25" t="s">
+        <v>46152</v>
+      </c>
+      <c r="S29" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T29" s="28"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-    </row>
-    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="T29" s="30"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:22">
+      <c r="A30" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="17">
         <v>26</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="19">
         <v>26</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17">
+      <c r="I30" s="19"/>
+      <c r="J30" s="19">
         <v>70</v>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="6" t="str">
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="6" t="str">
+      <c r="N30" s="24">
+        <v>46151</v>
+      </c>
+      <c r="O30" s="24">
+        <v>46151</v>
+      </c>
+      <c r="P30" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q30" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R30" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S30" s="25" t="s">
+        <v>46153</v>
+      </c>
+      <c r="S30" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T30" s="28"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-    </row>
-    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="T30" s="30"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:22">
+      <c r="A31" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="17">
         <v>27</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="19">
         <v>27</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17">
+      <c r="I31" s="19"/>
+      <c r="J31" s="19">
         <v>70</v>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="6" t="str">
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="6" t="str">
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q31" s="28" t="s">
+      <c r="Q31" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R31" s="26" t="str">
+      <c r="R31" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S31" s="25" t="s">
+      <c r="S31" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T31" s="28"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-    </row>
-    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="T31" s="30"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:22">
+      <c r="A32" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="17">
         <v>28</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="19">
         <v>28</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17">
+      <c r="I32" s="19"/>
+      <c r="J32" s="19">
         <v>70</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="6" t="str">
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="6" t="str">
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="Q32" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R32" s="26" t="str">
+      <c r="R32" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S32" s="25" t="s">
+      <c r="S32" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T32" s="28"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-    </row>
-    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="T32" s="30"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:22">
+      <c r="A33" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="17">
         <v>29</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="19">
         <v>29</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17">
+      <c r="I33" s="19"/>
+      <c r="J33" s="19">
         <v>70</v>
       </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="6" t="str">
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="6" t="str">
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q33" s="28" t="s">
+      <c r="Q33" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R33" s="26" t="str">
+      <c r="R33" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S33" s="25" t="s">
+      <c r="S33" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T33" s="28"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
-    </row>
-    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="T33" s="30"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:22">
+      <c r="A34" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="17">
         <v>30</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="19">
         <v>30</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17">
+      <c r="I34" s="19"/>
+      <c r="J34" s="19">
         <v>70</v>
       </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="6" t="str">
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="6" t="str">
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q34" s="28" t="s">
+      <c r="Q34" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R34" s="26" t="str">
+      <c r="R34" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S34" s="25" t="s">
+      <c r="S34" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T34" s="28"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-    </row>
-    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="T34" s="30"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:22">
+      <c r="A35" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="17">
         <v>31</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="19">
         <v>31</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17">
+      <c r="I35" s="19"/>
+      <c r="J35" s="19">
         <v>70</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="6" t="str">
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="6" t="str">
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q35" s="28" t="s">
+      <c r="Q35" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R35" s="26" t="str">
+      <c r="R35" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S35" s="25" t="s">
+      <c r="S35" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T35" s="28"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-    </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="T35" s="30"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:22">
+      <c r="A36" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="17">
         <v>32</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="19">
         <v>32</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17">
+      <c r="I36" s="19"/>
+      <c r="J36" s="19">
         <v>70</v>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="6" t="str">
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="6" t="str">
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q36" s="28" t="s">
+      <c r="Q36" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R36" s="26" t="str">
+      <c r="R36" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S36" s="25" t="s">
+      <c r="S36" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T36" s="28"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-    </row>
-    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="T36" s="30"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:22">
+      <c r="A37" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="17">
         <v>33</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="19">
         <v>33</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17">
+      <c r="I37" s="19"/>
+      <c r="J37" s="19">
         <v>70</v>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="6" t="str">
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="6" t="str">
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q37" s="28" t="s">
+      <c r="Q37" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R37" s="26" t="str">
+      <c r="R37" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S37" s="25" t="s">
+      <c r="S37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T37" s="28"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-    </row>
-    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="T37" s="30"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:22">
+      <c r="A38" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="17">
         <v>34</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="19">
         <v>34</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17">
+      <c r="I38" s="19"/>
+      <c r="J38" s="19">
         <v>70</v>
       </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="6" t="str">
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="6" t="str">
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q38" s="28" t="s">
+      <c r="Q38" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R38" s="26" t="str">
+      <c r="R38" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S38" s="25" t="s">
+      <c r="S38" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T38" s="28"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-    </row>
-    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="T38" s="30"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:22">
+      <c r="A39" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="17">
         <v>35</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="19">
         <v>35</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17">
+      <c r="I39" s="19"/>
+      <c r="J39" s="19">
         <v>70</v>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="6" t="str">
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="6" t="str">
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q39" s="28" t="s">
+      <c r="Q39" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R39" s="26" t="str">
+      <c r="R39" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S39" s="25" t="s">
+      <c r="S39" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T39" s="28"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
-    </row>
-    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="T39" s="30"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:22">
+      <c r="A40" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="17">
         <v>36</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="19">
         <v>36</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17">
+      <c r="I40" s="19"/>
+      <c r="J40" s="19">
         <v>80</v>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="6" t="str">
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
-      <c r="P40" s="6" t="str">
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q40" s="28" t="s">
+      <c r="Q40" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R40" s="26" t="str">
+      <c r="R40" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S40" s="25" t="s">
+      <c r="S40" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T40" s="28"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-    </row>
-    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="T40" s="30"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:22">
+      <c r="A41" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="17">
         <v>37</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="19">
         <v>37</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17">
+      <c r="I41" s="19"/>
+      <c r="J41" s="19">
         <v>80</v>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="6" t="str">
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22"/>
-      <c r="P41" s="6" t="str">
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q41" s="28" t="s">
+      <c r="Q41" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R41" s="26" t="str">
+      <c r="R41" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S41" s="25" t="s">
+      <c r="S41" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T41" s="28"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-    </row>
-    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="T41" s="30"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:22">
+      <c r="A42" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="17">
         <v>38</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="19">
         <v>38</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17">
+      <c r="I42" s="19"/>
+      <c r="J42" s="19">
         <v>80</v>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="6" t="str">
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="6" t="str">
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q42" s="28" t="s">
+      <c r="Q42" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R42" s="26" t="str">
+      <c r="R42" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S42" s="25" t="s">
+      <c r="S42" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T42" s="28"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-    </row>
-    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="T42" s="30"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:22">
+      <c r="A43" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="17">
         <v>39</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="19">
         <v>39</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17">
+      <c r="I43" s="19"/>
+      <c r="J43" s="19">
         <v>80</v>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="6" t="str">
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="6" t="str">
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q43" s="28" t="s">
+      <c r="Q43" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R43" s="26" t="str">
+      <c r="R43" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S43" s="25" t="s">
+      <c r="S43" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T43" s="28"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-    </row>
-    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="T43" s="30"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:22">
+      <c r="A44" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="17">
         <v>40</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="19">
         <v>40</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17">
+      <c r="I44" s="19"/>
+      <c r="J44" s="19">
         <v>80</v>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="6" t="str">
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="6" t="str">
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q44" s="28" t="s">
+      <c r="Q44" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R44" s="26" t="str">
+      <c r="R44" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S44" s="25" t="s">
+      <c r="S44" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T44" s="28"/>
-      <c r="U44" s="27"/>
-      <c r="V44" s="27"/>
-    </row>
-    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="T44" s="30"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:22">
+      <c r="A45" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="17">
         <v>41</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="19">
         <v>41</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17">
+      <c r="I45" s="19"/>
+      <c r="J45" s="19">
         <v>80</v>
       </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="6" t="str">
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="6" t="str">
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q45" s="28" t="s">
+      <c r="Q45" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R45" s="26" t="str">
+      <c r="R45" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S45" s="25" t="s">
+      <c r="S45" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T45" s="28"/>
-      <c r="U45" s="27"/>
-      <c r="V45" s="27"/>
-    </row>
-    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="T45" s="30"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:22">
+      <c r="A46" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="17">
         <v>42</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="19">
         <v>42</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17">
+      <c r="I46" s="19"/>
+      <c r="J46" s="19">
         <v>70</v>
       </c>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="6" t="str">
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="6" t="str">
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="28" t="s">
+      <c r="Q46" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="26" t="str">
+      <c r="R46" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="25" t="s">
+      <c r="S46" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T46" s="28"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-    </row>
-    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="T46" s="30"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:22">
+      <c r="A47" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="17">
         <v>43</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="19">
         <v>43</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17">
+      <c r="I47" s="19"/>
+      <c r="J47" s="19">
         <v>70</v>
       </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="6" t="str">
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="6" t="str">
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="28" t="s">
+      <c r="Q47" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="26" t="str">
+      <c r="R47" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="25" t="s">
+      <c r="S47" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T47" s="28"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-    </row>
-    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="T47" s="30"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:22">
+      <c r="A48" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="21">
         <v>44</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="23">
         <v>44</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="23">
         <v>50</v>
       </c>
-      <c r="J48" s="21"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="6" t="str">
+      <c r="J48" s="23"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="23" t="str">
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="25" t="s">
+      <c r="Q48" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="26" t="str">
+      <c r="R48" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="29" t="s">
+      <c r="S48" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T48" s="29"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000001000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
+      <formula1>Protocol!$J$1:$J$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
+      <formula1>Protocol!$K$1:$K$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$J$1:$J$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q5:Q48</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$K$1:$K$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>T5:T48</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5060,778 +5493,772 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" ht="30" spans="1:7">
+      <c r="A4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" ht="30" spans="1:7">
+      <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" ht="30" spans="1:7">
+      <c r="A6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" ht="30" spans="1:7">
+      <c r="A7" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" ht="30" spans="1:7">
+      <c r="A8" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>21</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" ht="30" spans="1:7">
+      <c r="A9" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>24</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" ht="30" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>25</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" ht="30" spans="1:7">
+      <c r="A11" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>2</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" ht="30" spans="1:7">
+      <c r="A12" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" ht="30" spans="1:7">
+      <c r="A13" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="9">
         <v>5</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" ht="30" spans="1:7">
+      <c r="A14" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>6</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" ht="30" spans="1:7">
+      <c r="A15" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>8</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>3</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>10</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" ht="30" spans="1:7">
+      <c r="A19" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" ht="30" spans="1:7">
+      <c r="A20" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="30" spans="1:7">
+      <c r="A21" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>18</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" ht="30" spans="1:7">
+      <c r="A22" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" ht="30" spans="1:7">
+      <c r="A23" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" ht="30" spans="1:7">
+      <c r="A24" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>30</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" ht="30" spans="1:7">
+      <c r="A25" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="9">
         <v>11</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" ht="30" spans="1:7">
+      <c r="A26" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="9">
         <v>13</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" ht="30" spans="1:7">
+      <c r="A27" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="9">
         <v>14</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" ht="30" spans="1:7">
+      <c r="A28" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <v>26</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" ht="30" spans="1:7">
+      <c r="A29" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="9">
         <v>27</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" ht="30" spans="1:7">
+      <c r="A30" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="9">
         <v>28</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" ht="30" spans="1:7">
+      <c r="A31" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="9">
         <v>23</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" ht="30" spans="1:7">
+      <c r="A32" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="9">
         <v>29</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" ht="30" spans="1:7">
+      <c r="A33" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="9">
         <v>33</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" ht="30" spans="1:7">
+      <c r="A34" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="9">
         <v>31</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" ht="30" spans="1:7">
+      <c r="A35" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="9">
         <v>32</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="11" t="s">
         <v>82</v>
       </c>
     </row>
@@ -5839,13 +6266,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5853,9 +6280,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5867,1165 +6295,1147 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:10">
+      <c r="A5" s="4">
         <v>46114</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6" t="str">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4">
         <v>46115</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6" t="str">
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4">
         <v>46118</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6" t="str">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4">
         <v>46119</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6" t="str">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4">
         <v>46120</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6" t="str">
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4">
         <v>46121</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6" t="str">
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="str">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="str">
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="str">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6" t="str">
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="str">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6" t="str">
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="str">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6" t="str">
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3" t="str">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="str">
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="str">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6" t="str">
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3" t="str">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6" t="str">
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="str">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6" t="str">
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="str">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6" t="str">
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3" t="str">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6" t="str">
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3" t="str">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6" t="str">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3" t="str">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6" t="str">
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3" t="str">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6" t="str">
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3" t="str">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6" t="str">
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3" t="str">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6" t="str">
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="str">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6" t="str">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3" t="str">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6" t="str">
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="str">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6" t="str">
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3" t="str">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6" t="str">
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3" t="str">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6" t="str">
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3" t="str">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6" t="str">
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3" t="str">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6" t="str">
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3" t="str">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="str">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3" t="str">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6" t="str">
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3" t="str">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6" t="str">
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3" t="str">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6" t="str">
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3" t="str">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6" t="str">
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3" t="str">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6" t="str">
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3" t="str">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6" t="str">
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3" t="str">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6" t="str">
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3" t="str">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6" t="str">
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3" t="str">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6" t="str">
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3" t="str">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6" t="str">
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3" t="str">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6" t="str">
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3" t="str">
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6" t="str">
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3" t="str">
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6" t="str">
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3" t="str">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6" t="str">
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3" t="str">
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6" t="str">
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3" t="str">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6" t="str">
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3" t="str">
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6" t="str">
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3" t="str">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6" t="str">
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3" t="str">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6" t="str">
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3" t="str">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6" t="str">
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3" t="str">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6" t="str">
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3" t="str">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6" t="str">
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="3" t="str">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6" t="str">
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3" t="str">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6" t="str">
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3" t="str">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6" t="str">
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3" t="str">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6" t="str">
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3" t="str">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6" t="str">
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3" t="str">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6" t="str">
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3" t="str">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6" t="str">
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3" t="str">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6" t="str">
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3" t="str">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="6" t="str">
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_A5DF4AF97BFCDF16A895230763713F60AD1D3BD9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7AD2831-85A2-4D3A-B7B5-14BA33BBA826}"/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -13,39 +19,52 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -56,20 +75,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -892,17 +911,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,202 +929,58 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1118,8 +989,14 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,194 +1051,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1389,427 +1080,173 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1861,53 +1298,21 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1921,9 +1326,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1962,9 +1373,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3"/>
+        <xdr:cNvPr id="2" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2008,9 +1425,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3"/>
+        <xdr:cNvPr id="3" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2045,7 +1468,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2059,9 +1482,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2100,9 +1529,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2"/>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2146,9 +1581,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2"/>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2182,67 +1623,83 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Suggested Seq"/>
-    <tableColumn id="3" name="Type"/>
-    <tableColumn id="4" name="Chapter Part"/>
-    <tableColumn id="5" name="Topic / Task"/>
-    <tableColumn id="6" name="Goal" dataDxfId="0"/>
-    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
-    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
-    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
-    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
-    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
-    <tableColumn id="12" name="Read End" dataDxfId="6"/>
-    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
-    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
-    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
-    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
-    <tableColumn id="17" name="Status" dataDxfId="11"/>
-    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
-    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
-    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
-    <tableColumn id="21" name="Notes" dataDxfId="15"/>
-    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
+      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
+      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
+      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
+      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Exercises"/>
-    <tableColumn id="3" name="Topic Cluster"/>
-    <tableColumn id="4" name="Why this set matters"/>
-    <tableColumn id="5" name="Priority"/>
-    <tableColumn id="6" name="Suggested after"/>
-    <tableColumn id="7" name="Done?"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Date"/>
-    <tableColumn id="2" name="Day #"/>
-    <tableColumn id="3" name="Units touched"/>
-    <tableColumn id="4" name="Read min"/>
-    <tableColumn id="5" name="Ex min"/>
-    <tableColumn id="6" name="Actual total min"/>
-    <tableColumn id="7" name="Big takeaway"/>
-    <tableColumn id="8" name="Blocker"/>
-    <tableColumn id="9" name="Next action"/>
-    <tableColumn id="10" name="Mood / energy"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
+      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
+      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2418,227 +1875,233 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:4">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:4">
-      <c r="A5" s="36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="34">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="34">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:4">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>26</v>
-      </c>
-      <c r="C6" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="38" t="str">
+      <c r="D6" s="34" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:4">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>286.153846150085</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:4">
-      <c r="A8" s="36" t="s">
+        <v>195.78947368163713</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
+        <v>19</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="38">
+      <c r="D8" s="34">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:4">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="str">
+      <c r="D9" s="33" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:4">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.590909090909091</v>
-      </c>
-      <c r="C10" s="36" t="s">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="37" t="str">
+      <c r="D10" s="33" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:4">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:4">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:1">
-      <c r="A13" s="41" t="s">
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:4">
-      <c r="A15" s="42" t="s">
+    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4">
-      <c r="A17" s="42" t="s">
+    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="38">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>13</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="39" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2647,16 +2110,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2668,10 +2130,17 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2679,7 +2148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" spans="10:11">
+    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2687,17 +2156,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="31">
         <v>46114</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2707,7 +2176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="21.95" customHeight="1" spans="4:11">
+    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2718,10 +2187,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
         <v>40</v>
       </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2729,91 +2205,160 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A7" s="35" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A8" s="35" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A9" s="35" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A10" s="35" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+    </row>
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A11" s="35" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1"/>
-    <row r="13" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A13" s="34" t="s">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+    </row>
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A14" s="35" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+    </row>
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A15" s="35" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A16" s="35" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+    </row>
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
         <v>52</v>
       </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2829,2660 +2374,2718 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" ht="15.75"/>
-    <row r="4" ht="24" customHeight="1" spans="1:22">
-      <c r="A4" s="15" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:22">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="17">
         <v>60</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="8" t="str">
+      <c r="J5" s="17"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="6" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="8" t="str">
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="6" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="28" t="str">
+      <c r="R5" s="26" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" s="27"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:22">
-      <c r="A6" s="17" t="s">
+      <c r="S5" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="25"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+    </row>
+    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <v>2</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <v>60</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="8" t="str">
+      <c r="J6" s="17"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="Q6" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="28" t="str">
+      <c r="R6" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="27"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:22">
-      <c r="A7" s="17" t="s">
+      <c r="S6" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T6" s="25"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+    </row>
+    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <v>3</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <v>3</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <v>75</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="8" t="str">
+      <c r="J7" s="17"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="28" t="str">
+      <c r="R7" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:22">
-      <c r="A8" s="17" t="s">
+      <c r="S7" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T7" s="25"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+    </row>
+    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <v>4</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <v>75</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="8" t="str">
+      <c r="J8" s="17"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="27" t="s">
+      <c r="Q8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="28" t="str">
+      <c r="R8" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T8" s="27"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:22">
-      <c r="A9" s="17" t="s">
+      <c r="S8" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="25"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+    </row>
+    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <v>5</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17">
         <v>60</v>
       </c>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N9" s="24">
-        <v>46118.4166666667</v>
-      </c>
-      <c r="O9" s="24">
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <v>46118.416666666701</v>
+      </c>
+      <c r="O9" s="22">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="6">
         <f t="shared" si="1"/>
-        <v>479.999999951106</v>
-      </c>
-      <c r="Q9" s="30" t="s">
+        <v>479.99999995110556</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:22">
-      <c r="A10" s="17" t="s">
+      <c r="S9" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T9" s="28"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+    </row>
+    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>6</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="17">
         <v>6</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17">
         <v>60</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N10" s="24">
-        <v>46119.5416666667</v>
-      </c>
-      <c r="O10" s="24">
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N10" s="22">
+        <v>46119.541666666701</v>
+      </c>
+      <c r="O10" s="22">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="6">
         <f t="shared" si="1"/>
-        <v>119.999999951106</v>
-      </c>
-      <c r="Q10" s="30" t="s">
+        <v>119.99999995110556</v>
+      </c>
+      <c r="Q10" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="26">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:22">
-      <c r="A11" s="17" t="s">
+      <c r="S10" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T10" s="28"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+    </row>
+    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <v>7</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="17">
         <v>7</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17">
         <v>50</v>
       </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="8" t="str">
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="Q11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="28" t="str">
+      <c r="R11" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T11" s="30"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:22">
-      <c r="A12" s="17" t="s">
+      <c r="S11" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+    </row>
+    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="17">
         <v>8</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17">
         <v>50</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <v>46121.5833333333</v>
-      </c>
-      <c r="O12" s="24">
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <v>46121.583333333299</v>
+      </c>
+      <c r="O12" s="22">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="6">
         <f t="shared" si="1"/>
-        <v>240.000000048894</v>
-      </c>
-      <c r="Q12" s="30" t="s">
+        <v>240.00000004889444</v>
+      </c>
+      <c r="Q12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="26">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:22">
-      <c r="A13" s="17" t="s">
+      <c r="S12" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" s="28"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+    </row>
+    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <v>9</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="17">
         <v>9</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17">
         <v>50</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="8" t="str">
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="Q13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="28" t="str">
+      <c r="R13" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T13" s="30"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:22">
-      <c r="A14" s="17" t="s">
+      <c r="S13" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="28"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+    </row>
+    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="17">
         <v>10</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19">
+      <c r="I14" s="17"/>
+      <c r="J14" s="17">
         <v>60</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N14" s="24">
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N14" s="22">
         <v>46123</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="22">
         <v>46123</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="30" t="s">
+      <c r="Q14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="28">
+      <c r="R14" s="26">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:22">
-      <c r="A15" s="17" t="s">
+      <c r="S14" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+    </row>
+    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <v>11</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="17">
         <v>11</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19">
+      <c r="I15" s="17"/>
+      <c r="J15" s="17">
         <v>60</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N15" s="24">
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N15" s="22">
         <v>46124</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="22">
         <v>46126</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="6">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="30" t="s">
+      <c r="Q15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="26">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T15" s="30"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:22">
-      <c r="A16" s="21" t="s">
+      <c r="S15" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T15" s="28"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+    </row>
+    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>12</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="21">
         <v>12</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="21">
         <v>45</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="25" t="str">
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="28" t="str">
+      <c r="R16" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T16" s="31"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:22">
-      <c r="A17" s="17" t="s">
+      <c r="S16" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T16" s="29"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+    </row>
+    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <v>13</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="17">
         <v>13</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="17">
         <v>50</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="8" t="str">
+      <c r="J17" s="17"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="27" t="s">
+      <c r="Q17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="28" t="str">
+      <c r="R17" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T17" s="27"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:22">
-      <c r="A18" s="17" t="s">
+      <c r="S17" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T17" s="25"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+    </row>
+    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="15">
         <v>14</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="17">
         <v>14</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="17">
         <v>70</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="8" t="str">
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="27" t="s">
+      <c r="Q18" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="28" t="str">
+      <c r="R18" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T18" s="27"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:22">
-      <c r="A19" s="17" t="s">
+      <c r="S18" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T18" s="25"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+    </row>
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="15">
         <v>15</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="17">
         <v>15</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <v>80</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="8" t="str">
+      <c r="J19" s="17"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="Q19" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="28" t="str">
+      <c r="R19" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T19" s="27"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:22">
-      <c r="A20" s="17" t="s">
+      <c r="S19" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T19" s="25"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+    </row>
+    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="15">
         <v>16</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="17">
         <v>16</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <v>60</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="8" t="str">
+      <c r="J20" s="17"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="27" t="s">
+      <c r="Q20" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="28" t="str">
+      <c r="R20" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T20" s="27"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:22">
-      <c r="A21" s="17" t="s">
+      <c r="S20" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T20" s="25"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+    </row>
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <v>17</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="17">
         <v>17</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <v>80</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="8" t="str">
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q21" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="28" t="str">
+      <c r="R21" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T21" s="27"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:22">
-      <c r="A22" s="17" t="s">
+      <c r="S21" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T21" s="25"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+    </row>
+    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="15">
         <v>18</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="17">
         <v>18</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="17">
         <v>80</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="8" t="str">
+      <c r="J22" s="17"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="27" t="s">
+      <c r="Q22" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="28" t="str">
+      <c r="R22" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T22" s="27"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:22">
-      <c r="A23" s="17" t="s">
+      <c r="S22" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T22" s="25"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+    </row>
+    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="15">
         <v>19</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="17">
         <v>19</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17">
         <v>60</v>
       </c>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N23" s="24">
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N23" s="22">
         <v>46143</v>
       </c>
-      <c r="O23" s="24">
+      <c r="O23" s="22">
         <v>46143</v>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="30" t="s">
+      <c r="Q23" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="28">
+      <c r="R23" s="26">
         <f t="shared" si="2"/>
         <v>46145</v>
       </c>
-      <c r="S23" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T23" s="30"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:22">
-      <c r="A24" s="17" t="s">
+      <c r="S23" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T23" s="28"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+    </row>
+    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <v>20</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="17">
         <v>20</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19">
+      <c r="I24" s="17"/>
+      <c r="J24" s="17">
         <v>60</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N24" s="24">
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N24" s="22">
         <v>46144</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="22">
         <v>46144</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="30" t="s">
+      <c r="Q24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="28">
+      <c r="R24" s="26">
         <f t="shared" si="2"/>
         <v>46146</v>
       </c>
-      <c r="S24" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T24" s="30"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:22">
-      <c r="A25" s="17" t="s">
+      <c r="S24" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T24" s="28"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+    </row>
+    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <v>21</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="17">
         <v>21</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19">
+      <c r="I25" s="17"/>
+      <c r="J25" s="17">
         <v>60</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N25" s="24">
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N25" s="22">
         <v>46145</v>
       </c>
-      <c r="O25" s="24">
+      <c r="O25" s="22">
         <v>46145</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="30" t="s">
+      <c r="Q25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="28">
+      <c r="R25" s="26">
         <f t="shared" si="2"/>
         <v>46147</v>
       </c>
-      <c r="S25" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T25" s="30"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:22">
-      <c r="A26" s="17" t="s">
+      <c r="S25" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T25" s="28"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+    </row>
+    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="15">
         <v>22</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="17">
         <v>22</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19">
+      <c r="I26" s="17"/>
+      <c r="J26" s="17">
         <v>60</v>
       </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N26" s="24">
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N26" s="22">
         <v>46147</v>
       </c>
-      <c r="O26" s="24">
+      <c r="O26" s="22">
         <v>46147</v>
       </c>
-      <c r="P26" s="8">
+      <c r="P26" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="30" t="s">
+      <c r="Q26" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="28">
+      <c r="R26" s="26">
         <f t="shared" si="2"/>
         <v>46149</v>
       </c>
-      <c r="S26" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T26" s="30"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:22">
-      <c r="A27" s="17" t="s">
+      <c r="S26" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T26" s="28"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+    </row>
+    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="15">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="17">
         <v>23</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19">
+      <c r="I27" s="17"/>
+      <c r="J27" s="17">
         <v>60</v>
       </c>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N27" s="24">
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N27" s="22">
         <v>46148</v>
       </c>
-      <c r="O27" s="24">
+      <c r="O27" s="22">
         <v>46148</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="30" t="s">
+      <c r="Q27" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="28">
+      <c r="R27" s="26">
         <f t="shared" si="2"/>
         <v>46150</v>
       </c>
-      <c r="S27" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T27" s="30"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:22">
-      <c r="A28" s="17" t="s">
+      <c r="S27" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T27" s="28"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+    </row>
+    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="15">
         <v>24</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="17">
         <v>24</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19">
+      <c r="I28" s="17"/>
+      <c r="J28" s="17">
         <v>70</v>
       </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N28" s="24">
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N28" s="22">
         <v>46149</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="22">
         <v>46149</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="30" t="s">
+      <c r="Q28" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="28">
+      <c r="R28" s="26">
         <f t="shared" si="2"/>
         <v>46151</v>
       </c>
-      <c r="S28" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T28" s="30"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:22">
-      <c r="A29" s="17" t="s">
+      <c r="S28" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T28" s="28"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+    </row>
+    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="15">
         <v>25</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="17">
         <v>25</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19">
+      <c r="I29" s="17"/>
+      <c r="J29" s="17">
         <v>70</v>
       </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N29" s="24">
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N29" s="22">
         <v>46150</v>
       </c>
-      <c r="O29" s="24">
+      <c r="O29" s="22">
         <v>46150</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="30" t="s">
+      <c r="Q29" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="28">
+      <c r="R29" s="26">
         <f t="shared" si="2"/>
         <v>46152</v>
       </c>
-      <c r="S29" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T29" s="30"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:22">
-      <c r="A30" s="17" t="s">
+      <c r="S29" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T29" s="28"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+    </row>
+    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="15">
         <v>26</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="17">
         <v>26</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19">
+      <c r="I30" s="17"/>
+      <c r="J30" s="17">
         <v>70</v>
       </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N30" s="24">
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N30" s="22">
         <v>46151</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="22">
         <v>46151</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="30" t="s">
+      <c r="Q30" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="28">
+      <c r="R30" s="26">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S30" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T30" s="30"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:22">
-      <c r="A31" s="17" t="s">
+      <c r="S30" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T30" s="28"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+    </row>
+    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="15">
         <v>27</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="17">
         <v>27</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19">
+      <c r="I31" s="17"/>
+      <c r="J31" s="17">
         <v>70</v>
       </c>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="8" t="str">
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N31" s="22">
+        <v>46151</v>
+      </c>
+      <c r="O31" s="22">
+        <v>46151</v>
+      </c>
+      <c r="P31" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q31" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R31" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S31" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T31" s="30"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:22">
-      <c r="A32" s="17" t="s">
+        <v>46153</v>
+      </c>
+      <c r="S31" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T31" s="28"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+    </row>
+    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="15">
         <v>28</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="17">
         <v>28</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19">
+      <c r="I32" s="17"/>
+      <c r="J32" s="17">
         <v>70</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="8" t="str">
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N32" s="22">
+        <v>46152</v>
+      </c>
+      <c r="O32" s="22">
+        <v>46152</v>
+      </c>
+      <c r="P32" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q32" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R32" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S32" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T32" s="30"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:22">
-      <c r="A33" s="17" t="s">
+        <v>46154</v>
+      </c>
+      <c r="S32" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T32" s="28"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+    </row>
+    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="15">
         <v>29</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="17">
         <v>29</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19">
+      <c r="I33" s="17"/>
+      <c r="J33" s="17">
         <v>70</v>
       </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="8" t="str">
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N33" s="22">
+        <v>46153</v>
+      </c>
+      <c r="O33" s="22">
+        <v>46153</v>
+      </c>
+      <c r="P33" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q33" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" s="26">
+        <f t="shared" si="2"/>
+        <v>46155</v>
+      </c>
+      <c r="S33" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T33" s="28"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="27"/>
+    </row>
+    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="15">
         <v>30</v>
       </c>
-      <c r="R33" s="28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S33" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T33" s="30"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:22">
-      <c r="A34" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B34" s="17">
+      <c r="C34" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="17">
         <v>30</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="G34" s="19">
-        <v>30</v>
-      </c>
-      <c r="H34" s="20">
+      <c r="H34" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19">
+      <c r="I34" s="17"/>
+      <c r="J34" s="17">
         <v>70</v>
       </c>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="8" t="str">
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N34" s="22">
+        <v>46154</v>
+      </c>
+      <c r="O34" s="22">
+        <v>46154</v>
+      </c>
+      <c r="P34" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q34" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R34" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S34" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T34" s="30"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:22">
-      <c r="A35" s="17" t="s">
+        <v>46156</v>
+      </c>
+      <c r="S34" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T34" s="28"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="27"/>
+    </row>
+    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="15">
         <v>31</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="17">
         <v>31</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19">
+      <c r="I35" s="17"/>
+      <c r="J35" s="17">
         <v>70</v>
       </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="8" t="str">
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N35" s="22">
+        <v>46154</v>
+      </c>
+      <c r="O35" s="22">
+        <v>46154</v>
+      </c>
+      <c r="P35" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q35" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R35" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S35" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T35" s="30"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:22">
-      <c r="A36" s="17" t="s">
+        <v>46156</v>
+      </c>
+      <c r="S35" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T35" s="28"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+    </row>
+    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="15">
         <v>32</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="17">
         <v>32</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19">
+      <c r="I36" s="17"/>
+      <c r="J36" s="17">
         <v>70</v>
       </c>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="8" t="str">
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N36" s="22">
+        <v>46154</v>
+      </c>
+      <c r="O36" s="22">
+        <v>46154</v>
+      </c>
+      <c r="P36" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q36" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R36" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S36" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T36" s="30"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:22">
-      <c r="A37" s="17" t="s">
+        <v>46156</v>
+      </c>
+      <c r="S36" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T36" s="28"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="27"/>
+    </row>
+    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="15">
         <v>33</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="17">
         <v>33</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19">
+      <c r="I37" s="17"/>
+      <c r="J37" s="17">
         <v>70</v>
       </c>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="8" t="str">
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q37" s="30" t="s">
+      <c r="Q37" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R37" s="28" t="str">
+      <c r="R37" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S37" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T37" s="30"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:22">
-      <c r="A38" s="17" t="s">
+      <c r="S37" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T37" s="28"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+    </row>
+    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="15">
         <v>34</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="17">
         <v>34</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19">
+      <c r="I38" s="17"/>
+      <c r="J38" s="17">
         <v>70</v>
       </c>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="8" t="str">
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q38" s="30" t="s">
+      <c r="Q38" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R38" s="28" t="str">
+      <c r="R38" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S38" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T38" s="30"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:22">
-      <c r="A39" s="17" t="s">
+      <c r="S38" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T38" s="28"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="27"/>
+    </row>
+    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="15">
         <v>35</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="17">
         <v>35</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19">
+      <c r="I39" s="17"/>
+      <c r="J39" s="17">
         <v>70</v>
       </c>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="8" t="str">
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q39" s="30" t="s">
+      <c r="Q39" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R39" s="28" t="str">
+      <c r="R39" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S39" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T39" s="30"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:22">
-      <c r="A40" s="17" t="s">
+      <c r="S39" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T39" s="28"/>
+      <c r="U39" s="27"/>
+      <c r="V39" s="27"/>
+    </row>
+    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="15">
         <v>36</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="17">
         <v>36</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19">
+      <c r="I40" s="17"/>
+      <c r="J40" s="17">
         <v>80</v>
       </c>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="8" t="str">
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q40" s="30" t="s">
+      <c r="Q40" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R40" s="28" t="str">
+      <c r="R40" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S40" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T40" s="30"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:22">
-      <c r="A41" s="17" t="s">
+      <c r="S40" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T40" s="28"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+    </row>
+    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="15">
         <v>37</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="17">
         <v>37</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19">
+      <c r="I41" s="17"/>
+      <c r="J41" s="17">
         <v>80</v>
       </c>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="8" t="str">
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q41" s="30" t="s">
+      <c r="Q41" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R41" s="28" t="str">
+      <c r="R41" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S41" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T41" s="30"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:22">
-      <c r="A42" s="17" t="s">
+      <c r="S41" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T41" s="28"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+    </row>
+    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="15">
         <v>38</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="17">
         <v>38</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19">
+      <c r="I42" s="17"/>
+      <c r="J42" s="17">
         <v>80</v>
       </c>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="8" t="str">
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q42" s="30" t="s">
+      <c r="Q42" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R42" s="28" t="str">
+      <c r="R42" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S42" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T42" s="30"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:22">
-      <c r="A43" s="17" t="s">
+      <c r="S42" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T42" s="28"/>
+      <c r="U42" s="27"/>
+      <c r="V42" s="27"/>
+    </row>
+    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="15">
         <v>39</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="17">
         <v>39</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19">
+      <c r="I43" s="17"/>
+      <c r="J43" s="17">
         <v>80</v>
       </c>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="8" t="str">
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q43" s="30" t="s">
+      <c r="Q43" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R43" s="28" t="str">
+      <c r="R43" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S43" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T43" s="30"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="1:22">
-      <c r="A44" s="17" t="s">
+      <c r="S43" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T43" s="28"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+    </row>
+    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="15">
         <v>40</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="17">
         <v>40</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H44" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19">
+      <c r="I44" s="17"/>
+      <c r="J44" s="17">
         <v>80</v>
       </c>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="8" t="str">
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q44" s="30" t="s">
+      <c r="Q44" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R44" s="28" t="str">
+      <c r="R44" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S44" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T44" s="30"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:22">
-      <c r="A45" s="17" t="s">
+      <c r="S44" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T44" s="28"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="27"/>
+    </row>
+    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="15">
         <v>41</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="17">
         <v>41</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19">
+      <c r="I45" s="17"/>
+      <c r="J45" s="17">
         <v>80</v>
       </c>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="8" t="str">
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q45" s="30" t="s">
+      <c r="Q45" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R45" s="28" t="str">
+      <c r="R45" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S45" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T45" s="30"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:22">
-      <c r="A46" s="17" t="s">
+      <c r="S45" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T45" s="28"/>
+      <c r="U45" s="27"/>
+      <c r="V45" s="27"/>
+    </row>
+    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="15">
         <v>42</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="17">
         <v>42</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19">
+      <c r="I46" s="17"/>
+      <c r="J46" s="17">
         <v>70</v>
       </c>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="8" t="str">
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="30" t="s">
+      <c r="Q46" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="28" t="str">
+      <c r="R46" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T46" s="30"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" spans="1:22">
-      <c r="A47" s="17" t="s">
+      <c r="S46" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T46" s="28"/>
+      <c r="U46" s="27"/>
+      <c r="V46" s="27"/>
+    </row>
+    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="15">
         <v>43</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="17">
         <v>43</v>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19">
+      <c r="I47" s="17"/>
+      <c r="J47" s="17">
         <v>70</v>
       </c>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="8" t="str">
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="30" t="s">
+      <c r="Q47" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="28" t="str">
+      <c r="R47" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="T47" s="30"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:22">
-      <c r="A48" s="21" t="s">
+      <c r="S47" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="T47" s="28"/>
+      <c r="U47" s="27"/>
+      <c r="V47" s="27"/>
+    </row>
+    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="19">
         <v>44</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="21">
         <v>44</v>
       </c>
-      <c r="H48" s="20">
+      <c r="H48" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="21">
         <v>50</v>
       </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="25" t="str">
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="27" t="s">
+      <c r="Q48" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="28" t="str">
+      <c r="R48" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="T48" s="31"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
+      <c r="S48" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="T48" s="29"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
-      <formula1>Protocol!$J$1:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
-      <formula1>Protocol!$K$1:$K$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$J$1:$J$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q5:Q48</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$K$1:$K$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>T5:T48</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5493,772 +5096,778 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" ht="30" spans="1:7">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:7">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>12</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" ht="30" spans="1:7">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="1:7">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="1:7">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" ht="30" spans="1:7">
-      <c r="A9" s="9" t="s">
+      <c r="G8" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" ht="30" spans="1:7">
-      <c r="A10" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>25</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" ht="30" spans="1:7">
-      <c r="A11" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" ht="30" spans="1:7">
-      <c r="A12" s="9" t="s">
+      <c r="G11" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>4</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" ht="30" spans="1:7">
-      <c r="A13" s="9" t="s">
+      <c r="G12" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>5</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:7">
-      <c r="A14" s="9" t="s">
+      <c r="G13" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <v>6</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:7">
-      <c r="A15" s="9" t="s">
+      <c r="G14" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>8</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="9" t="s">
+      <c r="G15" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9" t="s">
+      <c r="G16" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <v>9</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9" t="s">
+      <c r="G17" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <v>10</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="1:7">
-      <c r="A19" s="9" t="s">
+      <c r="G18" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <v>15</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="1:7">
-      <c r="A20" s="9" t="s">
+      <c r="G19" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="7">
         <v>16</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" ht="30" spans="1:7">
-      <c r="A21" s="9" t="s">
+      <c r="G20" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" ht="30" spans="1:7">
-      <c r="A22" s="9" t="s">
+      <c r="G21" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" ht="30" spans="1:7">
-      <c r="A23" s="9" t="s">
+      <c r="G22" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>22</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="1:7">
-      <c r="A24" s="9" t="s">
+      <c r="G23" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>30</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:7">
-      <c r="A25" s="9" t="s">
+      <c r="G24" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="1:7">
-      <c r="A26" s="9" t="s">
+      <c r="G25" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <v>13</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" ht="30" spans="1:7">
-      <c r="A27" s="9" t="s">
+      <c r="G26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="7">
         <v>14</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" ht="30" spans="1:7">
-      <c r="A28" s="9" t="s">
+      <c r="G27" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" ht="30" spans="1:7">
-      <c r="A29" s="9" t="s">
+      <c r="G28" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" ht="30" spans="1:7">
-      <c r="A30" s="9" t="s">
+      <c r="G29" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" ht="30" spans="1:7">
-      <c r="A31" s="9" t="s">
+      <c r="G30" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>23</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" ht="30" spans="1:7">
-      <c r="A32" s="9" t="s">
+      <c r="G31" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="9" t="s">
+      <c r="G32" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="7">
         <v>33</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="9" t="s">
+      <c r="G33" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <v>31</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" ht="30" spans="1:7">
-      <c r="A35" s="9" t="s">
+      <c r="G34" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="7">
         <v>32</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="9" t="s">
         <v>82</v>
       </c>
     </row>
@@ -6266,13 +5875,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6280,10 +5889,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -6295,1147 +5903,1165 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46114</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="str">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46115</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46118</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46119</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46120</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>46121</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="str">
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="str">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="str">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5" t="str">
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="str">
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="str">
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="str">
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="str">
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="str">
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="str">
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="str">
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="str">
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="str">
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="str">
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="str">
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="str">
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="str">
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="str">
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5" t="str">
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="str">
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="str">
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="str">
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5" t="str">
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5" t="str">
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5" t="str">
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5" t="str">
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5" t="str">
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="8" t="str">
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5" t="str">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8" t="str">
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5" t="str">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8" t="str">
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5" t="str">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8" t="str">
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5" t="str">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8" t="str">
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5" t="str">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8" t="str">
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5" t="str">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8" t="str">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5" t="str">
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="8" t="str">
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5" t="str">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="8" t="str">
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5" t="str">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8" t="str">
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5" t="str">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="8" t="str">
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5" t="str">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="8" t="str">
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5" t="str">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="8" t="str">
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5" t="str">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8" t="str">
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5" t="str">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8" t="str">
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5" t="str">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8" t="str">
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5" t="str">
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8" t="str">
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5" t="str">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8" t="str">
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5" t="str">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="8" t="str">
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="str">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8" t="str">
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5" t="str">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8" t="str">
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5" t="str">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8" t="str">
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5" t="str">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8" t="str">
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5" t="str">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8" t="str">
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5" t="str">
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8" t="str">
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5" t="str">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="8" t="str">
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="str">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="8" t="str">
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5" t="str">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8" t="str">
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_A5DF4AF97BFCDF16A895230763713F60AD1D3BD9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7AD2831-85A2-4D3A-B7B5-14BA33BBA826}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,52 +13,39 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -75,20 +56,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -911,13 +892,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,58 +914,202 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -989,14 +1118,8 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1051,8 +1174,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1080,173 +1389,427 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1298,21 +1861,53 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1326,15 +1921,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1373,15 +1962,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1425,15 +2008,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1468,7 +2045,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1482,15 +2059,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1529,15 +2100,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1581,15 +2146,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1623,83 +2182,67 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
-      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
-      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
-      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
-      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Suggested Seq"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Chapter Part"/>
+    <tableColumn id="5" name="Topic / Task"/>
+    <tableColumn id="6" name="Goal" dataDxfId="0"/>
+    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
+    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
+    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
+    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
+    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
+    <tableColumn id="12" name="Read End" dataDxfId="6"/>
+    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
+    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
+    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
+    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
+    <tableColumn id="17" name="Status" dataDxfId="11"/>
+    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
+    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
+    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
+    <tableColumn id="21" name="Notes" dataDxfId="15"/>
+    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Exercises"/>
+    <tableColumn id="3" name="Topic Cluster"/>
+    <tableColumn id="4" name="Why this set matters"/>
+    <tableColumn id="5" name="Priority"/>
+    <tableColumn id="6" name="Suggested after"/>
+    <tableColumn id="7" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
-      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
-      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Day #"/>
+    <tableColumn id="3" name="Units touched"/>
+    <tableColumn id="4" name="Read min"/>
+    <tableColumn id="5" name="Ex min"/>
+    <tableColumn id="6" name="Actual total min"/>
+    <tableColumn id="7" name="Big takeaway"/>
+    <tableColumn id="8" name="Blocker"/>
+    <tableColumn id="9" name="Next action"/>
+    <tableColumn id="10" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1875,233 +2418,227 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1" spans="1:4">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" ht="24" customHeight="1" spans="1:4">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:4">
+      <c r="A5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="38">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="38">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+    <row r="6" ht="24" customHeight="1" spans="1:4">
+      <c r="A6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>32</v>
-      </c>
-      <c r="C6" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="34" t="str">
+      <c r="D6" s="38" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:4">
+      <c r="A7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>195.78947368163713</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+        <v>177.142857140529</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:4">
+      <c r="A8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>19</v>
-      </c>
-      <c r="C8" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="38">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+    <row r="9" ht="24" customHeight="1" spans="1:4">
+      <c r="A9" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="33" t="str">
+      <c r="D9" s="37" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" ht="24" customHeight="1" spans="1:4">
+      <c r="A10" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="C10" s="32" t="s">
+        <v>0.772727272727273</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="33" t="str">
+      <c r="D10" s="37" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:4">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:4">
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:1">
+      <c r="A13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:4">
+      <c r="A15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+    <row r="16" ht="24" customHeight="1" spans="1:4">
+      <c r="A16" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="44" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:4">
+      <c r="A17" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="43">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="43">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>13</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="44" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2110,15 +2647,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2130,17 +2668,10 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2148,7 +2679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="21.95" customHeight="1" spans="10:11">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2156,17 +2687,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A3" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="33">
         <v>46114</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2176,7 +2707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="21.95" customHeight="1" spans="4:11">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2187,17 +2718,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+    <row r="5" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2205,160 +2729,91 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+    <row r="6" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+    </row>
+    <row r="7" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A7" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-    </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A8" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-    </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+    </row>
+    <row r="9" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-    </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+    </row>
+    <row r="10" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A10" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-    </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+    </row>
+    <row r="11" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A11" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-    </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+    </row>
+    <row r="12" ht="21.95" customHeight="1"/>
+    <row r="13" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A13" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-    </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+    </row>
+    <row r="14" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-    </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+    </row>
+    <row r="15" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A15" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-    </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+    </row>
+    <row r="16" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A16" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="10" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2374,2718 +2829,2692 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="15.75"/>
+    <row r="4" ht="24" customHeight="1" spans="1:22">
+      <c r="A4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="24" customHeight="1" spans="1:22">
+      <c r="A5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <v>1</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="19">
         <v>60</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="6" t="str">
+      <c r="J5" s="19"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="8" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="6" t="str">
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="8" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="26" t="str">
+      <c r="R5" s="28" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="25"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-    </row>
-    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="T5" s="27"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:22">
+      <c r="A6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="19">
         <v>2</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="19">
         <v>60</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="6" t="str">
+      <c r="J6" s="19"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="6" t="str">
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="26" t="str">
+      <c r="R6" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="S6" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T6" s="25"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-    </row>
-    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="T6" s="27"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:22">
+      <c r="A7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="19">
         <v>3</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="19">
         <v>75</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="6" t="str">
+      <c r="J7" s="19"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="6" t="str">
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="26" t="str">
+      <c r="R7" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T7" s="25"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-    </row>
-    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="T7" s="27"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:22">
+      <c r="A8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="19">
         <v>4</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="19">
         <v>75</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="6" t="str">
+      <c r="J8" s="19"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="6" t="str">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="Q8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="26" t="str">
+      <c r="R8" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="25" t="s">
+      <c r="S8" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="25"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-    </row>
-    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="T8" s="27"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:22">
+      <c r="A9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="17">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="19">
         <v>5</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17">
+      <c r="I9" s="19"/>
+      <c r="J9" s="19">
         <v>60</v>
       </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="6" t="str">
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N9" s="22">
-        <v>46118.416666666701</v>
-      </c>
-      <c r="O9" s="22">
+      <c r="N9" s="24">
+        <v>46118.4166666667</v>
+      </c>
+      <c r="O9" s="24">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="8">
         <f t="shared" si="1"/>
-        <v>479.99999995110556</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+        <v>479.999999951106</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="28">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="25" t="s">
+      <c r="S9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T9" s="28"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-    </row>
-    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="T9" s="30"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:22">
+      <c r="A10" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="17">
         <v>6</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="19">
         <v>6</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17">
+      <c r="I10" s="19"/>
+      <c r="J10" s="19">
         <v>60</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="6" t="str">
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N10" s="22">
-        <v>46119.541666666701</v>
-      </c>
-      <c r="O10" s="22">
+      <c r="N10" s="24">
+        <v>46119.5416666667</v>
+      </c>
+      <c r="O10" s="24">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="8">
         <f t="shared" si="1"/>
-        <v>119.99999995110556</v>
-      </c>
-      <c r="Q10" s="28" t="s">
+        <v>119.999999951106</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="28">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="25" t="s">
+      <c r="S10" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T10" s="28"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-    </row>
-    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="T10" s="30"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:22">
+      <c r="A11" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="17">
         <v>7</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="19">
         <v>7</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17">
+      <c r="I11" s="19"/>
+      <c r="J11" s="19">
         <v>50</v>
       </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="6" t="str">
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="6" t="str">
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="28" t="s">
+      <c r="Q11" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="26" t="str">
+      <c r="R11" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="25" t="s">
+      <c r="S11" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-    </row>
-    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="T11" s="30"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:22">
+      <c r="A12" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="17">
         <v>8</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <v>8</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17">
+      <c r="I12" s="19"/>
+      <c r="J12" s="19">
         <v>50</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="6" t="str">
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N12" s="22">
-        <v>46121.583333333299</v>
-      </c>
-      <c r="O12" s="22">
+      <c r="N12" s="24">
+        <v>46121.5833333333</v>
+      </c>
+      <c r="O12" s="24">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v>240.00000004889444</v>
-      </c>
-      <c r="Q12" s="28" t="s">
+        <v>240.000000048894</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="28">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="25" t="s">
+      <c r="S12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T12" s="28"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-    </row>
-    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="T12" s="30"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:22">
+      <c r="A13" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="17">
         <v>9</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <v>9</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17">
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
         <v>50</v>
       </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="6" t="str">
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="6" t="str">
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="28" t="s">
+      <c r="Q13" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="26" t="str">
+      <c r="R13" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="25" t="s">
+      <c r="S13" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T13" s="28"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-    </row>
-    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="T13" s="30"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:22">
+      <c r="A14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="17">
         <v>10</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="19">
         <v>10</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17">
+      <c r="I14" s="19"/>
+      <c r="J14" s="19">
         <v>60</v>
       </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="6" t="str">
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="24">
         <v>46123</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="24">
         <v>46123</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="28" t="s">
+      <c r="Q14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="28">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="25" t="s">
+      <c r="S14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-    </row>
-    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="T14" s="30"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:22">
+      <c r="A15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="17">
         <v>11</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <v>11</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17">
+      <c r="I15" s="19"/>
+      <c r="J15" s="19">
         <v>60</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="6" t="str">
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="24">
         <v>46124</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="24">
         <v>46126</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="8">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="28" t="s">
+      <c r="Q15" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="28">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="25" t="s">
+      <c r="S15" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-    </row>
-    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="T15" s="30"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:22">
+      <c r="A16" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
         <v>12</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="23">
         <v>12</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="23">
         <v>45</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="6" t="str">
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="23" t="str">
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="26" t="str">
+      <c r="R16" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="29" t="s">
+      <c r="S16" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T16" s="29"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-    </row>
-    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:22">
+      <c r="A17" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="17">
         <v>13</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="19">
         <v>13</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="19">
         <v>50</v>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="6" t="str">
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="6" t="str">
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="26" t="str">
+      <c r="R17" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="S17" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T17" s="25"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-    </row>
-    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="T17" s="27"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:22">
+      <c r="A18" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <v>14</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="19">
         <v>14</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="19">
         <v>70</v>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="6" t="str">
+      <c r="J18" s="19"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="6" t="str">
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="25" t="s">
+      <c r="Q18" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="26" t="str">
+      <c r="R18" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="25" t="s">
+      <c r="S18" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T18" s="25"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-    </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="T18" s="27"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:22">
+      <c r="A19" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="17">
         <v>15</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="19">
         <v>15</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="19">
         <v>80</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="6" t="str">
+      <c r="J19" s="19"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="6" t="str">
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="25" t="s">
+      <c r="Q19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="26" t="str">
+      <c r="R19" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="25" t="s">
+      <c r="S19" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T19" s="25"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-    </row>
-    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="T19" s="27"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:22">
+      <c r="A20" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="17">
         <v>16</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="19">
         <v>16</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="19">
         <v>60</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="6" t="str">
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="6" t="str">
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="26" t="str">
+      <c r="R20" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="25" t="s">
+      <c r="S20" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T20" s="25"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-    </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="T20" s="27"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:22">
+      <c r="A21" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="17">
         <v>17</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="19">
         <v>17</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="19">
         <v>80</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="6" t="str">
+      <c r="J21" s="19"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="6" t="str">
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="25" t="s">
+      <c r="Q21" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="26" t="str">
+      <c r="R21" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="25" t="s">
+      <c r="S21" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T21" s="25"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-    </row>
-    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="T21" s="27"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:22">
+      <c r="A22" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="17">
         <v>18</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="19">
         <v>18</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="19">
         <v>80</v>
       </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="6" t="str">
+      <c r="J22" s="19"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="6" t="str">
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="25" t="s">
+      <c r="Q22" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="26" t="str">
+      <c r="R22" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="25" t="s">
+      <c r="S22" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-    </row>
-    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="T22" s="27"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:22">
+      <c r="A23" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="17">
         <v>19</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="19">
         <v>19</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19">
         <v>60</v>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="6" t="str">
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="24">
         <v>46143</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="24">
         <v>46143</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="28" t="s">
+      <c r="Q23" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="28">
         <f t="shared" si="2"/>
         <v>46145</v>
       </c>
-      <c r="S23" s="25" t="s">
+      <c r="S23" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T23" s="28"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-    </row>
-    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="T23" s="30"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:22">
+      <c r="A24" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="17">
         <v>20</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="19">
         <v>20</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19">
         <v>60</v>
       </c>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="6" t="str">
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="24">
         <v>46144</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="24">
         <v>46144</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="28" t="s">
+      <c r="Q24" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="28">
         <f t="shared" si="2"/>
         <v>46146</v>
       </c>
-      <c r="S24" s="25" t="s">
+      <c r="S24" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T24" s="28"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-    </row>
-    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="T24" s="30"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:22">
+      <c r="A25" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="17">
         <v>21</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <v>21</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17">
+      <c r="I25" s="19"/>
+      <c r="J25" s="19">
         <v>60</v>
       </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="6" t="str">
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="24">
         <v>46145</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="24">
         <v>46145</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="28" t="s">
+      <c r="Q25" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="28">
         <f t="shared" si="2"/>
         <v>46147</v>
       </c>
-      <c r="S25" s="25" t="s">
+      <c r="S25" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T25" s="28"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-    </row>
-    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="T25" s="30"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:22">
+      <c r="A26" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <v>22</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="19">
         <v>22</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17">
+      <c r="I26" s="19"/>
+      <c r="J26" s="19">
         <v>60</v>
       </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="6" t="str">
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="24">
         <v>46147</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="24">
         <v>46147</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="28" t="s">
+      <c r="Q26" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="28">
         <f t="shared" si="2"/>
         <v>46149</v>
       </c>
-      <c r="S26" s="25" t="s">
+      <c r="S26" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T26" s="28"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-    </row>
-    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="T26" s="30"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:22">
+      <c r="A27" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="17">
         <v>23</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="19">
         <v>23</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17">
+      <c r="I27" s="19"/>
+      <c r="J27" s="19">
         <v>60</v>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="6" t="str">
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="24">
         <v>46148</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="24">
         <v>46148</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="28" t="s">
+      <c r="Q27" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="28">
         <f t="shared" si="2"/>
         <v>46150</v>
       </c>
-      <c r="S27" s="25" t="s">
+      <c r="S27" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T27" s="28"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-    </row>
-    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="T27" s="30"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:22">
+      <c r="A28" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="17">
         <v>24</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="19">
         <v>24</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17">
+      <c r="I28" s="19"/>
+      <c r="J28" s="19">
         <v>70</v>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="6" t="str">
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="24">
         <v>46149</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="24">
         <v>46149</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="28" t="s">
+      <c r="Q28" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="28">
         <f t="shared" si="2"/>
         <v>46151</v>
       </c>
-      <c r="S28" s="25" t="s">
+      <c r="S28" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T28" s="28"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-    </row>
-    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="T28" s="30"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:22">
+      <c r="A29" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="17">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="19">
         <v>25</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17">
+      <c r="I29" s="19"/>
+      <c r="J29" s="19">
         <v>70</v>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="6" t="str">
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N29" s="22">
+      <c r="N29" s="24">
         <v>46150</v>
       </c>
-      <c r="O29" s="22">
+      <c r="O29" s="24">
         <v>46150</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="28" t="s">
+      <c r="Q29" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="28">
         <f t="shared" si="2"/>
         <v>46152</v>
       </c>
-      <c r="S29" s="25" t="s">
+      <c r="S29" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T29" s="28"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-    </row>
-    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="T29" s="30"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:22">
+      <c r="A30" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="17">
         <v>26</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="19">
         <v>26</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17">
+      <c r="I30" s="19"/>
+      <c r="J30" s="19">
         <v>70</v>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="6" t="str">
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N30" s="22">
+      <c r="N30" s="24">
         <v>46151</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="24">
         <v>46151</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="28" t="s">
+      <c r="Q30" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="28">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S30" s="25" t="s">
+      <c r="S30" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T30" s="28"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-    </row>
-    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="T30" s="30"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:22">
+      <c r="A31" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="17">
         <v>27</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="19">
         <v>27</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17">
+      <c r="I31" s="19"/>
+      <c r="J31" s="19">
         <v>70</v>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="6" t="str">
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="24">
         <v>46151</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="24">
         <v>46151</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="28" t="s">
+      <c r="Q31" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="28">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S31" s="25" t="s">
+      <c r="S31" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T31" s="28"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-    </row>
-    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="T31" s="30"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:22">
+      <c r="A32" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="17">
         <v>28</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="19">
         <v>28</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17">
+      <c r="I32" s="19"/>
+      <c r="J32" s="19">
         <v>70</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="6" t="str">
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N32" s="22">
+      <c r="N32" s="24">
         <v>46152</v>
       </c>
-      <c r="O32" s="22">
+      <c r="O32" s="24">
         <v>46152</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="Q32" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="28">
         <f t="shared" si="2"/>
         <v>46154</v>
       </c>
-      <c r="S32" s="25" t="s">
+      <c r="S32" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T32" s="28"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-    </row>
-    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="T32" s="30"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:22">
+      <c r="A33" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="17">
         <v>29</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="19">
         <v>29</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17">
+      <c r="I33" s="19"/>
+      <c r="J33" s="19">
         <v>70</v>
       </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="6" t="str">
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N33" s="22">
+      <c r="N33" s="24">
         <v>46153</v>
       </c>
-      <c r="O33" s="22">
+      <c r="O33" s="24">
         <v>46153</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="28" t="s">
+      <c r="Q33" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="28">
         <f t="shared" si="2"/>
         <v>46155</v>
       </c>
-      <c r="S33" s="25" t="s">
+      <c r="S33" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T33" s="28"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
-    </row>
-    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="T33" s="30"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:22">
+      <c r="A34" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="17">
         <v>30</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="19">
         <v>30</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17">
+      <c r="I34" s="19"/>
+      <c r="J34" s="19">
         <v>70</v>
       </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="6" t="str">
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N34" s="22">
+      <c r="N34" s="24">
         <v>46154</v>
       </c>
-      <c r="O34" s="22">
+      <c r="O34" s="24">
         <v>46154</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="28" t="s">
+      <c r="Q34" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S34" s="25" t="s">
+      <c r="S34" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T34" s="28"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-    </row>
-    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="T34" s="30"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:22">
+      <c r="A35" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="17">
         <v>31</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="19">
         <v>31</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17">
+      <c r="I35" s="19"/>
+      <c r="J35" s="19">
         <v>70</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="6" t="str">
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="24">
         <v>46154</v>
       </c>
-      <c r="O35" s="22">
+      <c r="O35" s="24">
         <v>46154</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="28" t="s">
+      <c r="Q35" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S35" s="25" t="s">
+      <c r="S35" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T35" s="28"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-    </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="T35" s="30"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:22">
+      <c r="A36" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="17">
         <v>32</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="19">
         <v>32</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17">
+      <c r="I36" s="19"/>
+      <c r="J36" s="19">
         <v>70</v>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="6" t="str">
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N36" s="22">
+      <c r="N36" s="24">
         <v>46154</v>
       </c>
-      <c r="O36" s="22">
+      <c r="O36" s="24">
         <v>46154</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="28" t="s">
+      <c r="Q36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S36" s="25" t="s">
+      <c r="S36" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T36" s="28"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-    </row>
-    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="T36" s="30"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:22">
+      <c r="A37" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="17">
         <v>33</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="19">
         <v>33</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17">
+      <c r="I37" s="19"/>
+      <c r="J37" s="19">
         <v>70</v>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="6" t="str">
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="6" t="str">
+      <c r="N37" s="24">
+        <v>46159</v>
+      </c>
+      <c r="O37" s="24">
+        <v>46159</v>
+      </c>
+      <c r="P37" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q37" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R37" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S37" s="25" t="s">
+        <v>46161</v>
+      </c>
+      <c r="S37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T37" s="28"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-    </row>
-    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="T37" s="30"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:22">
+      <c r="A38" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="17">
         <v>34</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="19">
         <v>34</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17">
+      <c r="I38" s="19"/>
+      <c r="J38" s="19">
         <v>70</v>
       </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="6" t="str">
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="6" t="str">
+      <c r="N38" s="24">
+        <v>46160</v>
+      </c>
+      <c r="O38" s="24">
+        <v>46160</v>
+      </c>
+      <c r="P38" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q38" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R38" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S38" s="25" t="s">
+        <v>46162</v>
+      </c>
+      <c r="S38" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T38" s="28"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-    </row>
-    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="T38" s="30"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:22">
+      <c r="A39" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="17">
         <v>35</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="19">
         <v>35</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17">
+      <c r="I39" s="19"/>
+      <c r="J39" s="19">
         <v>70</v>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="6" t="str">
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="6" t="str">
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q39" s="28" t="s">
+      <c r="Q39" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R39" s="26" t="str">
+      <c r="R39" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S39" s="25" t="s">
+      <c r="S39" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T39" s="28"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
-    </row>
-    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="T39" s="30"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:22">
+      <c r="A40" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="17">
         <v>36</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="19">
         <v>36</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17">
+      <c r="I40" s="19"/>
+      <c r="J40" s="19">
         <v>80</v>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="6" t="str">
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
-      <c r="P40" s="6" t="str">
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q40" s="28" t="s">
+      <c r="Q40" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R40" s="26" t="str">
+      <c r="R40" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S40" s="25" t="s">
+      <c r="S40" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T40" s="28"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-    </row>
-    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="T40" s="30"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:22">
+      <c r="A41" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="17">
         <v>37</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="19">
         <v>37</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17">
+      <c r="I41" s="19"/>
+      <c r="J41" s="19">
         <v>80</v>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="6" t="str">
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22"/>
-      <c r="P41" s="6" t="str">
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q41" s="28" t="s">
+      <c r="Q41" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R41" s="26" t="str">
+      <c r="R41" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S41" s="25" t="s">
+      <c r="S41" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T41" s="28"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-    </row>
-    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="T41" s="30"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:22">
+      <c r="A42" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="17">
         <v>38</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="19">
         <v>38</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17">
+      <c r="I42" s="19"/>
+      <c r="J42" s="19">
         <v>80</v>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="6" t="str">
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="6" t="str">
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q42" s="28" t="s">
+      <c r="Q42" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R42" s="26" t="str">
+      <c r="R42" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S42" s="25" t="s">
+      <c r="S42" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T42" s="28"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-    </row>
-    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="T42" s="30"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:22">
+      <c r="A43" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="17">
         <v>39</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="19">
         <v>39</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17">
+      <c r="I43" s="19"/>
+      <c r="J43" s="19">
         <v>80</v>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="6" t="str">
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="6" t="str">
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q43" s="28" t="s">
+      <c r="Q43" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R43" s="26" t="str">
+      <c r="R43" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S43" s="25" t="s">
+      <c r="S43" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T43" s="28"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-    </row>
-    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="T43" s="30"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:22">
+      <c r="A44" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="17">
         <v>40</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="19">
         <v>40</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17">
+      <c r="I44" s="19"/>
+      <c r="J44" s="19">
         <v>80</v>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="6" t="str">
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="6" t="str">
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q44" s="28" t="s">
+      <c r="Q44" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R44" s="26" t="str">
+      <c r="R44" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S44" s="25" t="s">
+      <c r="S44" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T44" s="28"/>
-      <c r="U44" s="27"/>
-      <c r="V44" s="27"/>
-    </row>
-    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="T44" s="30"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:22">
+      <c r="A45" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="17">
         <v>41</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="19">
         <v>41</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17">
+      <c r="I45" s="19"/>
+      <c r="J45" s="19">
         <v>80</v>
       </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="6" t="str">
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="6" t="str">
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q45" s="28" t="s">
+      <c r="Q45" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R45" s="26" t="str">
+      <c r="R45" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S45" s="25" t="s">
+      <c r="S45" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T45" s="28"/>
-      <c r="U45" s="27"/>
-      <c r="V45" s="27"/>
-    </row>
-    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="T45" s="30"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:22">
+      <c r="A46" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="17">
         <v>42</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="19">
         <v>42</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17">
+      <c r="I46" s="19"/>
+      <c r="J46" s="19">
         <v>70</v>
       </c>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="6" t="str">
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="6" t="str">
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="28" t="s">
+      <c r="Q46" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="26" t="str">
+      <c r="R46" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="25" t="s">
+      <c r="S46" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T46" s="28"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-    </row>
-    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="T46" s="30"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:22">
+      <c r="A47" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="17">
         <v>43</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="19">
         <v>43</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17">
+      <c r="I47" s="19"/>
+      <c r="J47" s="19">
         <v>70</v>
       </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="6" t="str">
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="6" t="str">
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="28" t="s">
+      <c r="Q47" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="26" t="str">
+      <c r="R47" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="25" t="s">
+      <c r="S47" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T47" s="28"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-    </row>
-    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="T47" s="30"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:22">
+      <c r="A48" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="21">
         <v>44</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="23">
         <v>44</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="23">
         <v>50</v>
       </c>
-      <c r="J48" s="21"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="6" t="str">
+      <c r="J48" s="23"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="23" t="str">
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="25" t="s">
+      <c r="Q48" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="26" t="str">
+      <c r="R48" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="29" t="s">
+      <c r="S48" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T48" s="29"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000002000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
+      <formula1>Protocol!$J$1:$J$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
       <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
+      <formula1>Protocol!$K$1:$K$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$J$1:$J$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q5:Q48</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$K$1:$K$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>T5:T48</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5096,778 +5525,772 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" ht="30" spans="1:7">
+      <c r="A4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" ht="30" spans="1:7">
+      <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" ht="30" spans="1:7">
+      <c r="A6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" ht="30" spans="1:7">
+      <c r="A7" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" ht="30" spans="1:7">
+      <c r="A8" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>21</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" ht="30" spans="1:7">
+      <c r="A9" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>24</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" ht="30" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>25</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" ht="30" spans="1:7">
+      <c r="A11" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>2</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" ht="30" spans="1:7">
+      <c r="A12" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" ht="30" spans="1:7">
+      <c r="A13" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="9">
         <v>5</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" ht="30" spans="1:7">
+      <c r="A14" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>6</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" ht="30" spans="1:7">
+      <c r="A15" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>8</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>3</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>10</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" ht="30" spans="1:7">
+      <c r="A19" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" ht="30" spans="1:7">
+      <c r="A20" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="30" spans="1:7">
+      <c r="A21" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>18</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" ht="30" spans="1:7">
+      <c r="A22" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" ht="30" spans="1:7">
+      <c r="A23" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" ht="30" spans="1:7">
+      <c r="A24" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>30</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" ht="30" spans="1:7">
+      <c r="A25" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="9">
         <v>11</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" ht="30" spans="1:7">
+      <c r="A26" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="9">
         <v>13</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" ht="30" spans="1:7">
+      <c r="A27" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="9">
         <v>14</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" ht="30" spans="1:7">
+      <c r="A28" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <v>26</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" ht="30" spans="1:7">
+      <c r="A29" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="9">
         <v>27</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" ht="30" spans="1:7">
+      <c r="A30" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="9">
         <v>28</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" ht="30" spans="1:7">
+      <c r="A31" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="9">
         <v>23</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" ht="30" spans="1:7">
+      <c r="A32" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="9">
         <v>29</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" ht="30" spans="1:7">
+      <c r="A33" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="9">
         <v>33</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" ht="30" spans="1:7">
+      <c r="A34" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="9">
         <v>31</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" ht="30" spans="1:7">
+      <c r="A35" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="9">
         <v>32</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="11" t="s">
         <v>82</v>
       </c>
     </row>
@@ -5875,13 +6298,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5889,9 +6312,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5903,1165 +6327,1147 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:10">
+      <c r="A5" s="4">
         <v>46114</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6" t="str">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4">
         <v>46115</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6" t="str">
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4">
         <v>46118</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6" t="str">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4">
         <v>46119</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6" t="str">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4">
         <v>46120</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6" t="str">
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4">
         <v>46121</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6" t="str">
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="str">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="str">
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="str">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6" t="str">
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="str">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6" t="str">
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="str">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6" t="str">
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3" t="str">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="str">
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="str">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6" t="str">
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3" t="str">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6" t="str">
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="str">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6" t="str">
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="str">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6" t="str">
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3" t="str">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6" t="str">
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3" t="str">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6" t="str">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3" t="str">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6" t="str">
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3" t="str">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6" t="str">
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3" t="str">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6" t="str">
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3" t="str">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6" t="str">
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="str">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6" t="str">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3" t="str">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6" t="str">
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="str">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6" t="str">
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3" t="str">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6" t="str">
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3" t="str">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6" t="str">
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3" t="str">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6" t="str">
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3" t="str">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6" t="str">
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3" t="str">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="str">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3" t="str">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6" t="str">
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3" t="str">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6" t="str">
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3" t="str">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6" t="str">
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3" t="str">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6" t="str">
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3" t="str">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6" t="str">
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3" t="str">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6" t="str">
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3" t="str">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6" t="str">
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3" t="str">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6" t="str">
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3" t="str">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6" t="str">
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3" t="str">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6" t="str">
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3" t="str">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6" t="str">
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3" t="str">
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6" t="str">
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3" t="str">
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6" t="str">
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3" t="str">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6" t="str">
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3" t="str">
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6" t="str">
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3" t="str">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6" t="str">
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3" t="str">
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6" t="str">
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3" t="str">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6" t="str">
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3" t="str">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6" t="str">
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3" t="str">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6" t="str">
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3" t="str">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6" t="str">
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3" t="str">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6" t="str">
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="3" t="str">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6" t="str">
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3" t="str">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6" t="str">
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3" t="str">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6" t="str">
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3" t="str">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6" t="str">
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3" t="str">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6" t="str">
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3" t="str">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6" t="str">
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3" t="str">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6" t="str">
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3" t="str">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6" t="str">
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3" t="str">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="6" t="str">
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -894,15 +894,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,13 +950,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -968,24 +961,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -999,78 +976,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1090,10 +998,87 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1107,6 +1092,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1176,121 +1169,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1302,31 +1181,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1344,7 +1199,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1357,6 +1332,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1393,6 +1386,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -1410,6 +1412,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1455,24 +1466,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1493,10 +1486,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1505,136 +1498,136 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1658,10 +1651,10 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1670,7 +1663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1678,10 +1671,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1690,46 +1683,46 @@
     <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1738,22 +1731,22 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2464,7 +2457,7 @@
       </c>
       <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4">
@@ -2489,7 +2482,7 @@
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>9</v>
@@ -2512,7 +2505,7 @@
       </c>
       <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>177.142857140529</v>
+        <v>169.090909088687</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4">
@@ -2521,7 +2514,7 @@
       </c>
       <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>13</v>
@@ -2553,7 +2546,7 @@
       </c>
       <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.772727272727273</v>
+        <v>0.795454545454545</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>17</v>
@@ -4943,18 +4936,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="8" t="str">
+      <c r="N39" s="24">
+        <v>46161</v>
+      </c>
+      <c r="O39" s="24">
+        <v>46161</v>
+      </c>
+      <c r="P39" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R39" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R39" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46163</v>
       </c>
       <c r="S39" s="27" t="s">
         <v>82</v>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_C401529CABFDD34CA995230763713F90C79E3766" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3283CDC0-83F5-4E8B-BFAD-571BAE43B750}"/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -13,39 +19,52 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -56,20 +75,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <charset val="1"/>
             <scheme val="minor"/>
-            <charset val="1"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -892,17 +911,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,195 +929,51 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1111,8 +982,21 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1167,194 +1051,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1382,427 +1080,173 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1854,53 +1298,21 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1914,9 +1326,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1955,9 +1373,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3"/>
+        <xdr:cNvPr id="2" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2001,9 +1425,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3"/>
+        <xdr:cNvPr id="3" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2038,7 +1468,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2052,9 +1482,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2093,9 +1529,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2"/>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2139,9 +1581,15 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2"/>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2175,67 +1623,83 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Suggested Seq"/>
-    <tableColumn id="3" name="Type"/>
-    <tableColumn id="4" name="Chapter Part"/>
-    <tableColumn id="5" name="Topic / Task"/>
-    <tableColumn id="6" name="Goal" dataDxfId="0"/>
-    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
-    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
-    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
-    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
-    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
-    <tableColumn id="12" name="Read End" dataDxfId="6"/>
-    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
-    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
-    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
-    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
-    <tableColumn id="17" name="Status" dataDxfId="11"/>
-    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
-    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
-    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
-    <tableColumn id="21" name="Notes" dataDxfId="15"/>
-    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
+      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
+      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
+      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
+      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="Unit ID"/>
-    <tableColumn id="2" name="Exercises"/>
-    <tableColumn id="3" name="Topic Cluster"/>
-    <tableColumn id="4" name="Why this set matters"/>
-    <tableColumn id="5" name="Priority"/>
-    <tableColumn id="6" name="Suggested after"/>
-    <tableColumn id="7" name="Done?"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Date"/>
-    <tableColumn id="2" name="Day #"/>
-    <tableColumn id="3" name="Units touched"/>
-    <tableColumn id="4" name="Read min"/>
-    <tableColumn id="5" name="Ex min"/>
-    <tableColumn id="6" name="Actual total min"/>
-    <tableColumn id="7" name="Big takeaway"/>
-    <tableColumn id="8" name="Blocker"/>
-    <tableColumn id="9" name="Next action"/>
-    <tableColumn id="10" name="Mood / energy"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
+      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
+      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2411,227 +1875,233 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:4">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="34">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:4">
-      <c r="A5" s="36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="34">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="34">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:4">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="34">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>35</v>
-      </c>
-      <c r="C6" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="38" t="str">
+      <c r="D6" s="34" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:4">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="34">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>169.090909088687</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:4">
-      <c r="A8" s="36" t="s">
+        <v>137.77777777596688</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>22</v>
-      </c>
-      <c r="C8" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="34">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:4">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="34">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="37" t="str">
+      <c r="D9" s="33" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:4">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="35">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.795454545454545</v>
-      </c>
-      <c r="C10" s="36" t="s">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="37" t="str">
+      <c r="D10" s="33" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:4">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:4">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:1">
-      <c r="A13" s="41" t="s">
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:4">
-      <c r="A15" s="42" t="s">
+    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4">
-      <c r="A16" s="42" t="s">
+    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="38">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="38">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4">
-      <c r="A17" s="42" t="s">
+    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="38">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>13</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="39" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2640,16 +2110,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2661,10 +2130,17 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2672,7 +2148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" spans="10:11">
+    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2680,17 +2156,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="31">
         <v>46114</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2700,7 +2176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="21.95" customHeight="1" spans="4:11">
+    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2711,10 +2187,17 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" ht="21.95" customHeight="1" spans="1:11">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
         <v>40</v>
       </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2722,56 +2205,126 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A7" s="35" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A8" s="35" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A9" s="35" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A10" s="35" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+    </row>
+    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A11" s="35" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" ht="21.95" customHeight="1"/>
-    <row r="13" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A13" s="34" t="s">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+    </row>
+    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A14" s="35" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+    </row>
+    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A15" s="35" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" ht="21.95" customHeight="1" spans="1:1">
-      <c r="A16" s="35" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+    </row>
+    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
         <v>52</v>
       </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2780,33 +2333,32 @@
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2822,2696 +2374,2750 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" ht="15.75"/>
-    <row r="4" ht="24" customHeight="1" spans="1:22">
-      <c r="A4" s="15" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="P4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:22">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="17">
         <v>60</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="8" t="str">
+      <c r="J5" s="17"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="6" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="8" t="str">
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="6" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="28" t="str">
+      <c r="R5" s="26" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="27" t="s">
+      <c r="S5" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="27"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:22">
-      <c r="A6" s="17" t="s">
+      <c r="T5" s="25"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+    </row>
+    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <v>2</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <v>60</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="8" t="str">
+      <c r="J6" s="17"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="Q6" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="28" t="str">
+      <c r="R6" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="27" t="s">
+      <c r="S6" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T6" s="27"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:22">
-      <c r="A7" s="17" t="s">
+      <c r="T6" s="25"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+    </row>
+    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="15">
         <v>3</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <v>3</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <v>75</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="8" t="str">
+      <c r="J7" s="17"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="28" t="str">
+      <c r="R7" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="27" t="s">
+      <c r="S7" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:22">
-      <c r="A8" s="17" t="s">
+      <c r="T7" s="25"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+    </row>
+    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <v>4</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <v>75</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="8" t="str">
+      <c r="J8" s="17"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="27" t="s">
+      <c r="Q8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="28" t="str">
+      <c r="R8" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="27" t="s">
+      <c r="S8" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="27"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:22">
-      <c r="A9" s="17" t="s">
+      <c r="T8" s="25"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+    </row>
+    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="15">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <v>5</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17">
         <v>60</v>
       </c>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N9" s="24">
-        <v>46118.4166666667</v>
-      </c>
-      <c r="O9" s="24">
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <v>46118.416666666701</v>
+      </c>
+      <c r="O9" s="22">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="6">
         <f t="shared" si="1"/>
-        <v>479.999999951106</v>
-      </c>
-      <c r="Q9" s="30" t="s">
+        <v>479.99999995110556</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="27" t="s">
+      <c r="S9" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:22">
-      <c r="A10" s="17" t="s">
+      <c r="T9" s="28"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+    </row>
+    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>6</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="17">
         <v>6</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17">
         <v>60</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N10" s="24">
-        <v>46119.5416666667</v>
-      </c>
-      <c r="O10" s="24">
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N10" s="22">
+        <v>46119.541666666701</v>
+      </c>
+      <c r="O10" s="22">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="6">
         <f t="shared" si="1"/>
-        <v>119.999999951106</v>
-      </c>
-      <c r="Q10" s="30" t="s">
+        <v>119.99999995110556</v>
+      </c>
+      <c r="Q10" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="26">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="27" t="s">
+      <c r="S10" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:22">
-      <c r="A11" s="17" t="s">
+      <c r="T10" s="28"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+    </row>
+    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="15">
         <v>7</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="17">
         <v>7</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17">
         <v>50</v>
       </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="8" t="str">
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="Q11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="28" t="str">
+      <c r="R11" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="27" t="s">
+      <c r="S11" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T11" s="30"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:22">
-      <c r="A12" s="17" t="s">
+      <c r="T11" s="28"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+    </row>
+    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="17">
         <v>8</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17">
         <v>50</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <v>46121.5833333333</v>
-      </c>
-      <c r="O12" s="24">
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <v>46121.583333333299</v>
+      </c>
+      <c r="O12" s="22">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="6">
         <f t="shared" si="1"/>
-        <v>240.000000048894</v>
-      </c>
-      <c r="Q12" s="30" t="s">
+        <v>240.00000004889444</v>
+      </c>
+      <c r="Q12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="26">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="27" t="s">
+      <c r="S12" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:22">
-      <c r="A13" s="17" t="s">
+      <c r="T12" s="28"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+    </row>
+    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <v>9</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="17">
         <v>9</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17">
         <v>50</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="8" t="str">
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="Q13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="28" t="str">
+      <c r="R13" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="27" t="s">
+      <c r="S13" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T13" s="30"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:22">
-      <c r="A14" s="17" t="s">
+      <c r="T13" s="28"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+    </row>
+    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="15">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="17">
         <v>10</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19">
+      <c r="I14" s="17"/>
+      <c r="J14" s="17">
         <v>60</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N14" s="24">
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N14" s="22">
         <v>46123</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="22">
         <v>46123</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="30" t="s">
+      <c r="Q14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="28">
+      <c r="R14" s="26">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="27" t="s">
+      <c r="S14" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:22">
-      <c r="A15" s="17" t="s">
+      <c r="T14" s="28"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+    </row>
+    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <v>11</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="17">
         <v>11</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19">
+      <c r="I15" s="17"/>
+      <c r="J15" s="17">
         <v>60</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N15" s="24">
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N15" s="22">
         <v>46124</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="22">
         <v>46126</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="6">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="30" t="s">
+      <c r="Q15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="26">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="27" t="s">
+      <c r="S15" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T15" s="30"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:22">
-      <c r="A16" s="21" t="s">
+      <c r="T15" s="28"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+    </row>
+    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>12</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="21">
         <v>12</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="21">
         <v>45</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="25" t="str">
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="28" t="str">
+      <c r="R16" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="31" t="s">
+      <c r="S16" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="T16" s="31"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:22">
-      <c r="A17" s="17" t="s">
+      <c r="T16" s="29"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+    </row>
+    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <v>13</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="17">
         <v>13</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="17">
         <v>50</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="8" t="str">
+      <c r="J17" s="17"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="27" t="s">
+      <c r="Q17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="28" t="str">
+      <c r="R17" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="27" t="s">
+      <c r="S17" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T17" s="27"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:22">
-      <c r="A18" s="17" t="s">
+      <c r="T17" s="25"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+    </row>
+    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="15">
         <v>14</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="17">
         <v>14</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="17">
         <v>70</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="8" t="str">
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="27" t="s">
+      <c r="Q18" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="28" t="str">
+      <c r="R18" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="27" t="s">
+      <c r="S18" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T18" s="27"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:22">
-      <c r="A19" s="17" t="s">
+      <c r="T18" s="25"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+    </row>
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="15">
         <v>15</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="17">
         <v>15</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <v>80</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="8" t="str">
+      <c r="J19" s="17"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="Q19" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="28" t="str">
+      <c r="R19" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="27" t="s">
+      <c r="S19" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T19" s="27"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:22">
-      <c r="A20" s="17" t="s">
+      <c r="T19" s="25"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+    </row>
+    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="15">
         <v>16</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="17">
         <v>16</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="17">
         <v>60</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="8" t="str">
+      <c r="J20" s="17"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="27" t="s">
+      <c r="Q20" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="28" t="str">
+      <c r="R20" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="27" t="s">
+      <c r="S20" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T20" s="27"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:22">
-      <c r="A21" s="17" t="s">
+      <c r="T20" s="25"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+    </row>
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <v>17</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="17">
         <v>17</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="17">
         <v>80</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="8" t="str">
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q21" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="28" t="str">
+      <c r="R21" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="27" t="s">
+      <c r="S21" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T21" s="27"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:22">
-      <c r="A22" s="17" t="s">
+      <c r="T21" s="25"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+    </row>
+    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="15">
         <v>18</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="17">
         <v>18</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="17">
         <v>80</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="8" t="str">
+      <c r="J22" s="17"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="27" t="s">
+      <c r="Q22" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="28" t="str">
+      <c r="R22" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="27" t="s">
+      <c r="S22" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T22" s="27"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:22">
-      <c r="A23" s="17" t="s">
+      <c r="T22" s="25"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+    </row>
+    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="15">
         <v>19</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="17">
         <v>19</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17">
         <v>60</v>
       </c>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N23" s="24">
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N23" s="22">
         <v>46143</v>
       </c>
-      <c r="O23" s="24">
+      <c r="O23" s="22">
         <v>46143</v>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="30" t="s">
+      <c r="Q23" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="28">
+      <c r="R23" s="26">
         <f t="shared" si="2"/>
         <v>46145</v>
       </c>
-      <c r="S23" s="27" t="s">
+      <c r="S23" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T23" s="30"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:22">
-      <c r="A24" s="17" t="s">
+      <c r="T23" s="28"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+    </row>
+    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <v>20</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="17">
         <v>20</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19">
+      <c r="I24" s="17"/>
+      <c r="J24" s="17">
         <v>60</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N24" s="24">
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N24" s="22">
         <v>46144</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="22">
         <v>46144</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="30" t="s">
+      <c r="Q24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="28">
+      <c r="R24" s="26">
         <f t="shared" si="2"/>
         <v>46146</v>
       </c>
-      <c r="S24" s="27" t="s">
+      <c r="S24" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T24" s="30"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:22">
-      <c r="A25" s="17" t="s">
+      <c r="T24" s="28"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+    </row>
+    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <v>21</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="17">
         <v>21</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19">
+      <c r="I25" s="17"/>
+      <c r="J25" s="17">
         <v>60</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N25" s="24">
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N25" s="22">
         <v>46145</v>
       </c>
-      <c r="O25" s="24">
+      <c r="O25" s="22">
         <v>46145</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="30" t="s">
+      <c r="Q25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="28">
+      <c r="R25" s="26">
         <f t="shared" si="2"/>
         <v>46147</v>
       </c>
-      <c r="S25" s="27" t="s">
+      <c r="S25" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T25" s="30"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:22">
-      <c r="A26" s="17" t="s">
+      <c r="T25" s="28"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+    </row>
+    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="15">
         <v>22</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="17">
         <v>22</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19">
+      <c r="I26" s="17"/>
+      <c r="J26" s="17">
         <v>60</v>
       </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N26" s="24">
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N26" s="22">
         <v>46147</v>
       </c>
-      <c r="O26" s="24">
+      <c r="O26" s="22">
         <v>46147</v>
       </c>
-      <c r="P26" s="8">
+      <c r="P26" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="30" t="s">
+      <c r="Q26" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="28">
+      <c r="R26" s="26">
         <f t="shared" si="2"/>
         <v>46149</v>
       </c>
-      <c r="S26" s="27" t="s">
+      <c r="S26" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T26" s="30"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:22">
-      <c r="A27" s="17" t="s">
+      <c r="T26" s="28"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+    </row>
+    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="15">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="17">
         <v>23</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19">
+      <c r="I27" s="17"/>
+      <c r="J27" s="17">
         <v>60</v>
       </c>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N27" s="24">
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N27" s="22">
         <v>46148</v>
       </c>
-      <c r="O27" s="24">
+      <c r="O27" s="22">
         <v>46148</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="30" t="s">
+      <c r="Q27" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="28">
+      <c r="R27" s="26">
         <f t="shared" si="2"/>
         <v>46150</v>
       </c>
-      <c r="S27" s="27" t="s">
+      <c r="S27" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T27" s="30"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:22">
-      <c r="A28" s="17" t="s">
+      <c r="T27" s="28"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+    </row>
+    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="15">
         <v>24</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="17">
         <v>24</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19">
+      <c r="I28" s="17"/>
+      <c r="J28" s="17">
         <v>70</v>
       </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N28" s="24">
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N28" s="22">
         <v>46149</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="22">
         <v>46149</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="30" t="s">
+      <c r="Q28" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="28">
+      <c r="R28" s="26">
         <f t="shared" si="2"/>
         <v>46151</v>
       </c>
-      <c r="S28" s="27" t="s">
+      <c r="S28" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T28" s="30"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:22">
-      <c r="A29" s="17" t="s">
+      <c r="T28" s="28"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+    </row>
+    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="15">
         <v>25</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="17">
         <v>25</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19">
+      <c r="I29" s="17"/>
+      <c r="J29" s="17">
         <v>70</v>
       </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N29" s="24">
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N29" s="22">
         <v>46150</v>
       </c>
-      <c r="O29" s="24">
+      <c r="O29" s="22">
         <v>46150</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="30" t="s">
+      <c r="Q29" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="28">
+      <c r="R29" s="26">
         <f t="shared" si="2"/>
         <v>46152</v>
       </c>
-      <c r="S29" s="27" t="s">
+      <c r="S29" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T29" s="30"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:22">
-      <c r="A30" s="17" t="s">
+      <c r="T29" s="28"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+    </row>
+    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="15">
         <v>26</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="17">
         <v>26</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19">
+      <c r="I30" s="17"/>
+      <c r="J30" s="17">
         <v>70</v>
       </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N30" s="24">
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N30" s="22">
         <v>46151</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="22">
         <v>46151</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="30" t="s">
+      <c r="Q30" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="28">
+      <c r="R30" s="26">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S30" s="27" t="s">
+      <c r="S30" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T30" s="30"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:22">
-      <c r="A31" s="17" t="s">
+      <c r="T30" s="28"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+    </row>
+    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="15">
         <v>27</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="17">
         <v>27</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19">
+      <c r="I31" s="17"/>
+      <c r="J31" s="17">
         <v>70</v>
       </c>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N31" s="24">
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N31" s="22">
         <v>46151</v>
       </c>
-      <c r="O31" s="24">
+      <c r="O31" s="22">
         <v>46151</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P31" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="30" t="s">
+      <c r="Q31" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R31" s="28">
+      <c r="R31" s="26">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S31" s="27" t="s">
+      <c r="S31" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T31" s="30"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:22">
-      <c r="A32" s="17" t="s">
+      <c r="T31" s="28"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+    </row>
+    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="15">
         <v>28</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="17">
         <v>28</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19">
+      <c r="I32" s="17"/>
+      <c r="J32" s="17">
         <v>70</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N32" s="24">
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N32" s="22">
         <v>46152</v>
       </c>
-      <c r="O32" s="24">
+      <c r="O32" s="22">
         <v>46152</v>
       </c>
-      <c r="P32" s="8">
+      <c r="P32" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="30" t="s">
+      <c r="Q32" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="28">
+      <c r="R32" s="26">
         <f t="shared" si="2"/>
         <v>46154</v>
       </c>
-      <c r="S32" s="27" t="s">
+      <c r="S32" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T32" s="30"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:22">
-      <c r="A33" s="17" t="s">
+      <c r="T32" s="28"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+    </row>
+    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="15">
         <v>29</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="17">
         <v>29</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19">
+      <c r="I33" s="17"/>
+      <c r="J33" s="17">
         <v>70</v>
       </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N33" s="24">
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N33" s="22">
         <v>46153</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="22">
         <v>46153</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P33" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="30" t="s">
+      <c r="Q33" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R33" s="28">
+      <c r="R33" s="26">
         <f t="shared" si="2"/>
         <v>46155</v>
       </c>
-      <c r="S33" s="27" t="s">
+      <c r="S33" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T33" s="30"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:22">
-      <c r="A34" s="17" t="s">
+      <c r="T33" s="28"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="27"/>
+    </row>
+    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="15">
         <v>30</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="17">
         <v>30</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19">
+      <c r="I34" s="17"/>
+      <c r="J34" s="17">
         <v>70</v>
       </c>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N34" s="24">
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N34" s="22">
         <v>46154</v>
       </c>
-      <c r="O34" s="24">
+      <c r="O34" s="22">
         <v>46154</v>
       </c>
-      <c r="P34" s="8">
+      <c r="P34" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="30" t="s">
+      <c r="Q34" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R34" s="28">
+      <c r="R34" s="26">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S34" s="27" t="s">
+      <c r="S34" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T34" s="30"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:22">
-      <c r="A35" s="17" t="s">
+      <c r="T34" s="28"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="27"/>
+    </row>
+    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="15">
         <v>31</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="17">
         <v>31</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19">
+      <c r="I35" s="17"/>
+      <c r="J35" s="17">
         <v>70</v>
       </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N35" s="24">
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N35" s="22">
         <v>46154</v>
       </c>
-      <c r="O35" s="24">
+      <c r="O35" s="22">
         <v>46154</v>
       </c>
-      <c r="P35" s="8">
+      <c r="P35" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="30" t="s">
+      <c r="Q35" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R35" s="28">
+      <c r="R35" s="26">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S35" s="27" t="s">
+      <c r="S35" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T35" s="30"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:22">
-      <c r="A36" s="17" t="s">
+      <c r="T35" s="28"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+    </row>
+    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="15">
         <v>32</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="17">
         <v>32</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19">
+      <c r="I36" s="17"/>
+      <c r="J36" s="17">
         <v>70</v>
       </c>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N36" s="24">
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N36" s="22">
         <v>46154</v>
       </c>
-      <c r="O36" s="24">
+      <c r="O36" s="22">
         <v>46154</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="30" t="s">
+      <c r="Q36" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R36" s="28">
+      <c r="R36" s="26">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S36" s="27" t="s">
+      <c r="S36" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T36" s="30"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:22">
-      <c r="A37" s="17" t="s">
+      <c r="T36" s="28"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="27"/>
+    </row>
+    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="15">
         <v>33</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="17">
         <v>33</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19">
+      <c r="I37" s="17"/>
+      <c r="J37" s="17">
         <v>70</v>
       </c>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N37" s="24">
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N37" s="22">
         <v>46159</v>
       </c>
-      <c r="O37" s="24">
+      <c r="O37" s="22">
         <v>46159</v>
       </c>
-      <c r="P37" s="8">
+      <c r="P37" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="30" t="s">
+      <c r="Q37" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R37" s="28">
+      <c r="R37" s="26">
         <f t="shared" si="2"/>
         <v>46161</v>
       </c>
-      <c r="S37" s="27" t="s">
+      <c r="S37" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T37" s="30"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:22">
-      <c r="A38" s="17" t="s">
+      <c r="T37" s="28"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+    </row>
+    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="15">
         <v>34</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="17">
         <v>34</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19">
+      <c r="I38" s="17"/>
+      <c r="J38" s="17">
         <v>70</v>
       </c>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N38" s="24">
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N38" s="22">
         <v>46160</v>
       </c>
-      <c r="O38" s="24">
+      <c r="O38" s="22">
         <v>46160</v>
       </c>
-      <c r="P38" s="8">
+      <c r="P38" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="30" t="s">
+      <c r="Q38" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R38" s="28">
+      <c r="R38" s="26">
         <f t="shared" si="2"/>
         <v>46162</v>
       </c>
-      <c r="S38" s="27" t="s">
+      <c r="S38" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T38" s="30"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:22">
-      <c r="A39" s="17" t="s">
+      <c r="T38" s="28"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="27"/>
+    </row>
+    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="15">
         <v>35</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="17">
         <v>35</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19">
+      <c r="I39" s="17"/>
+      <c r="J39" s="17">
         <v>70</v>
       </c>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N39" s="24">
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N39" s="22">
         <v>46161</v>
       </c>
-      <c r="O39" s="24">
+      <c r="O39" s="22">
         <v>46161</v>
       </c>
-      <c r="P39" s="8">
+      <c r="P39" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="30" t="s">
+      <c r="Q39" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R39" s="28">
+      <c r="R39" s="26">
         <f t="shared" si="2"/>
         <v>46163</v>
       </c>
-      <c r="S39" s="27" t="s">
+      <c r="S39" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T39" s="30"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:22">
-      <c r="A40" s="17" t="s">
+      <c r="T39" s="28"/>
+      <c r="U39" s="27"/>
+      <c r="V39" s="27"/>
+    </row>
+    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="15">
         <v>36</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="17">
         <v>36</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19">
+      <c r="I40" s="17"/>
+      <c r="J40" s="17">
         <v>80</v>
       </c>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="8" t="str">
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N40" s="22">
+        <v>46162</v>
+      </c>
+      <c r="O40" s="22">
+        <v>46162</v>
+      </c>
+      <c r="P40" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q40" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R40" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S40" s="27" t="s">
+        <v>46164</v>
+      </c>
+      <c r="S40" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T40" s="30"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:22">
-      <c r="A41" s="17" t="s">
+      <c r="T40" s="28"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+    </row>
+    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="15">
         <v>37</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="17">
         <v>37</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19">
+      <c r="I41" s="17"/>
+      <c r="J41" s="17">
         <v>80</v>
       </c>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="8" t="str">
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N41" s="22">
+        <v>46163</v>
+      </c>
+      <c r="O41" s="22">
+        <v>46163</v>
+      </c>
+      <c r="P41" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q41" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R41" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S41" s="27" t="s">
+        <v>46165</v>
+      </c>
+      <c r="S41" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T41" s="30"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:22">
-      <c r="A42" s="17" t="s">
+      <c r="T41" s="28"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+    </row>
+    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="15">
         <v>38</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="17">
         <v>38</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19">
+      <c r="I42" s="17"/>
+      <c r="J42" s="17">
         <v>80</v>
       </c>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="8" t="str">
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N42" s="22">
+        <v>46164</v>
+      </c>
+      <c r="O42" s="22">
+        <v>46164</v>
+      </c>
+      <c r="P42" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q42" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R42" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S42" s="27" t="s">
+        <v>46166</v>
+      </c>
+      <c r="S42" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T42" s="30"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:22">
-      <c r="A43" s="17" t="s">
+      <c r="T42" s="28"/>
+      <c r="U42" s="27"/>
+      <c r="V42" s="27"/>
+    </row>
+    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="15">
         <v>39</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="17">
         <v>39</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19">
+      <c r="I43" s="17"/>
+      <c r="J43" s="17">
         <v>80</v>
       </c>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="8" t="str">
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N43" s="22">
+        <v>46165</v>
+      </c>
+      <c r="O43" s="22">
+        <v>46165</v>
+      </c>
+      <c r="P43" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q43" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R43" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S43" s="27" t="s">
+        <v>46167</v>
+      </c>
+      <c r="S43" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T43" s="30"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="1:22">
-      <c r="A44" s="17" t="s">
+      <c r="T43" s="28"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+    </row>
+    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="15">
         <v>40</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="17">
         <v>40</v>
       </c>
-      <c r="H44" s="20">
+      <c r="H44" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19">
+      <c r="I44" s="17"/>
+      <c r="J44" s="17">
         <v>80</v>
       </c>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="8" t="str">
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N44" s="22">
+        <v>46167</v>
+      </c>
+      <c r="O44" s="22">
+        <v>46167</v>
+      </c>
+      <c r="P44" s="6">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q44" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R44" s="28" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" s="26">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S44" s="27" t="s">
+        <v>46169</v>
+      </c>
+      <c r="S44" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T44" s="30"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="1:22">
-      <c r="A45" s="17" t="s">
+      <c r="T44" s="28"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="27"/>
+    </row>
+    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="15">
         <v>41</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="17">
         <v>41</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19">
+      <c r="I45" s="17"/>
+      <c r="J45" s="17">
         <v>80</v>
       </c>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="8" t="str">
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q45" s="30" t="s">
+      <c r="Q45" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R45" s="28" t="str">
+      <c r="R45" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S45" s="27" t="s">
+      <c r="S45" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T45" s="30"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:22">
-      <c r="A46" s="17" t="s">
+      <c r="T45" s="28"/>
+      <c r="U45" s="27"/>
+      <c r="V45" s="27"/>
+    </row>
+    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="15">
         <v>42</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="17">
         <v>42</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19">
+      <c r="I46" s="17"/>
+      <c r="J46" s="17">
         <v>70</v>
       </c>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="8" t="str">
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="30" t="s">
+      <c r="Q46" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="28" t="str">
+      <c r="R46" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="27" t="s">
+      <c r="S46" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T46" s="30"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" spans="1:22">
-      <c r="A47" s="17" t="s">
+      <c r="T46" s="28"/>
+      <c r="U46" s="27"/>
+      <c r="V46" s="27"/>
+    </row>
+    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="15">
         <v>43</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="17">
         <v>43</v>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19">
+      <c r="I47" s="17"/>
+      <c r="J47" s="17">
         <v>70</v>
       </c>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="8" t="str">
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="30" t="s">
+      <c r="Q47" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="28" t="str">
+      <c r="R47" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="27" t="s">
+      <c r="S47" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="T47" s="30"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:22">
-      <c r="A48" s="21" t="s">
+      <c r="T47" s="28"/>
+      <c r="U47" s="27"/>
+      <c r="V47" s="27"/>
+    </row>
+    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="19">
         <v>44</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="21">
         <v>44</v>
       </c>
-      <c r="H48" s="20">
+      <c r="H48" s="18">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="21">
         <v>50</v>
       </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="25" t="str">
+      <c r="J48" s="21"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="27" t="s">
+      <c r="Q48" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="28" t="str">
+      <c r="R48" s="26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="31" t="s">
+      <c r="S48" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="T48" s="31"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
-      <formula1>Protocol!$J$1:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
-      <formula1>Protocol!$K$1:$K$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$J$1:$J$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q5:Q48</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
+          <x14:formula1>
+            <xm:f>Protocol!$K$1:$K$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>T5:T48</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5522,772 +5128,778 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" ht="30" spans="1:7">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:7">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>12</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" ht="30" spans="1:7">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="1:7">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="1:7">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" ht="30" spans="1:7">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="1:7">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>25</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="1:7">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" ht="30" spans="1:7">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>4</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" ht="30" spans="1:7">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>5</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="1:7">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <v>6</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="1:7">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>8</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <v>9</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <v>10</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="1:7">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <v>15</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="1:7">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="7">
         <v>16</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" ht="30" spans="1:7">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" ht="30" spans="1:7">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="7">
         <v>20</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" ht="30" spans="1:7">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>22</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" ht="30" spans="1:7">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>30</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" ht="30" spans="1:7">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" ht="30" spans="1:7">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <v>13</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" ht="30" spans="1:7">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="7">
         <v>14</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" ht="30" spans="1:7">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="7">
         <v>26</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" ht="30" spans="1:7">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" ht="30" spans="1:7">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>28</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" ht="30" spans="1:7">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>23</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" ht="30" spans="1:7">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="7">
         <v>33</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <v>31</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" ht="30" spans="1:7">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="7">
         <v>32</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="9" t="s">
         <v>82</v>
       </c>
     </row>
@@ -6295,13 +5907,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -6309,10 +5921,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -6324,1147 +5935,1165 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46114</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="str">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46115</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46118</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46119</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46120</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>46121</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="str">
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="str">
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="str">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5" t="str">
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="str">
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="str">
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="str">
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="str">
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="str">
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="str">
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="str">
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="str">
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="str">
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="str">
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="str">
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="str">
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="str">
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="str">
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5" t="str">
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="str">
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="str">
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="str">
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5" t="str">
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5" t="str">
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5" t="str">
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5" t="str">
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5" t="str">
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="8" t="str">
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5" t="str">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8" t="str">
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5" t="str">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8" t="str">
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5" t="str">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8" t="str">
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5" t="str">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8" t="str">
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5" t="str">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8" t="str">
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5" t="str">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8" t="str">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5" t="str">
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="8" t="str">
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5" t="str">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="8" t="str">
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5" t="str">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8" t="str">
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5" t="str">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="8" t="str">
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5" t="str">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="8" t="str">
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5" t="str">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="8" t="str">
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5" t="str">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8" t="str">
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5" t="str">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8" t="str">
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5" t="str">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8" t="str">
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5" t="str">
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8" t="str">
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5" t="str">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8" t="str">
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5" t="str">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="8" t="str">
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="str">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8" t="str">
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5" t="str">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8" t="str">
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5" t="str">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8" t="str">
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5" t="str">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8" t="str">
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5" t="str">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8" t="str">
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5" t="str">
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8" t="str">
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5" t="str">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="8" t="str">
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="str">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="8" t="str">
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5" t="str">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8" t="str">
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/737d3273260deef1/learning_notes/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_C401529CABFDD34CA995230763713F90C79E3766" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3283CDC0-83F5-4E8B-BFAD-571BAE43B750}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19935" windowHeight="7785" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -19,52 +13,39 @@
     <sheet name="Exercise Map" sheetId="4" r:id="rId4"/>
     <sheet name="Daily Log" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Chapter 6 source file uploaded by user: /mnt/data/chap6.pdf</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>可选：如果你想用 Suggested Day 自动生成建议日期，就在这里填本章开始日期。</t>
         </r>
@@ -75,20 +56,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
+            <scheme val="minor"/>
             <charset val="1"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Built from the user's Chapter 6 PDF and the agreed study protocol. Source URL for Chapter 5 notes provided by user: https://archimondstat.github.io/resnick-notes/chap-5-integration-and-expectation.html</t>
         </r>
@@ -911,13 +892,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,51 +914,202 @@
       <b/>
       <sz val="15"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -982,21 +1118,8 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1051,8 +1174,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1080,173 +1389,427 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1298,21 +1861,53 @@
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1326,15 +1921,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1027" name="Text Box 3" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1373,15 +1962,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1425,15 +2008,9 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 3"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1468,7 +2045,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1482,15 +2059,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002080000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2050" name="Text Box 2" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1529,15 +2100,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1581,15 +2146,9 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="AutoShape 2"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1623,83 +2182,67 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
-  <autoFilter ref="A4:V48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitPlanTable" displayName="UnitPlanTable" ref="A4:V48">
+  <autoFilter ref="A4:V48"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Suggested Seq"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Chapter Part"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Topic / Task"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Goal" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Suggested Day" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Suggested Date" dataDxfId="19">
-      <calculatedColumnFormula>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Plan Read (min)" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Plan Ex (min)" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Read Start" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Read End" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Read Min" dataDxfId="14">
-      <calculatedColumnFormula>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ex Start" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ex End" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Ex Min" dataDxfId="11">
-      <calculatedColumnFormula>IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="C1 Due" dataDxfId="9">
-      <calculatedColumnFormula>IF(O5&lt;&gt;"",INT(O5)+2,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="C1 Done?" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Reproduce level" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Notes" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Link/Ref" dataDxfId="5"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Suggested Seq"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Chapter Part"/>
+    <tableColumn id="5" name="Topic / Task"/>
+    <tableColumn id="6" name="Goal" dataDxfId="0"/>
+    <tableColumn id="7" name="Suggested Day" dataDxfId="1"/>
+    <tableColumn id="8" name="Suggested Date" dataDxfId="2"/>
+    <tableColumn id="9" name="Plan Read (min)" dataDxfId="3"/>
+    <tableColumn id="10" name="Plan Ex (min)" dataDxfId="4"/>
+    <tableColumn id="11" name="Read Start" dataDxfId="5"/>
+    <tableColumn id="12" name="Read End" dataDxfId="6"/>
+    <tableColumn id="13" name="Read Min" dataDxfId="7"/>
+    <tableColumn id="14" name="Ex Start" dataDxfId="8"/>
+    <tableColumn id="15" name="Ex End" dataDxfId="9"/>
+    <tableColumn id="16" name="Ex Min" dataDxfId="10"/>
+    <tableColumn id="17" name="Status" dataDxfId="11"/>
+    <tableColumn id="18" name="C1 Due" dataDxfId="12"/>
+    <tableColumn id="19" name="C1 Done?" dataDxfId="13"/>
+    <tableColumn id="20" name="Reproduce level" dataDxfId="14"/>
+    <tableColumn id="21" name="Notes" dataDxfId="15"/>
+    <tableColumn id="22" name="Link/Ref" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
-  <autoFilter ref="A3:G35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ExerciseMapTable" displayName="ExerciseMapTable" ref="A3:G35">
+  <autoFilter ref="A3:G35"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Unit ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Exercises"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Topic Cluster"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Why this set matters"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Priority"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Suggested after"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Done?"/>
+    <tableColumn id="1" name="Unit ID"/>
+    <tableColumn id="2" name="Exercises"/>
+    <tableColumn id="3" name="Topic Cluster"/>
+    <tableColumn id="4" name="Why this set matters"/>
+    <tableColumn id="5" name="Priority"/>
+    <tableColumn id="6" name="Suggested after"/>
+    <tableColumn id="7" name="Done?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
-  <autoFilter ref="A4:J64" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DailyLogTable" displayName="DailyLogTable" ref="A4:J64">
+  <autoFilter ref="A4:J64"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Day #">
-      <calculatedColumnFormula>IF(A5="","",A5-Protocol!$B$3+1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Units touched"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Read min"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ex min"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Actual total min">
-      <calculatedColumnFormula>IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Big takeaway"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Blocker"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Next action"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Mood / energy"/>
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Day #"/>
+    <tableColumn id="3" name="Units touched"/>
+    <tableColumn id="4" name="Read min"/>
+    <tableColumn id="5" name="Ex min"/>
+    <tableColumn id="6" name="Actual total min"/>
+    <tableColumn id="7" name="Big takeaway"/>
+    <tableColumn id="8" name="Blocker"/>
+    <tableColumn id="9" name="Next action"/>
+    <tableColumn id="10" name="Mood / energy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1875,233 +2418,227 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1" spans="1:4">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" ht="24" customHeight="1" spans="1:4">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:4">
+      <c r="A5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="38">
         <f>COUNTA('Unit Plan'!A5:A48)</f>
         <v>44</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="38">
         <f>COUNTIF('Unit Plan'!T5:T48,"Independent")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+    <row r="6" ht="24" customHeight="1" spans="1:4">
+      <c r="A6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>40</v>
-      </c>
-      <c r="C6" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="34" t="str">
+      <c r="D6" s="38" t="str">
         <f>IFERROR(AVERAGE('Unit Plan'!M5:M48),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:4">
+      <c r="A7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Reading",'Unit Plan'!L5:L48,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>137.77777777596688</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+        <v>132.857142855397</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:4">
+      <c r="A8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>27</v>
-      </c>
-      <c r="C8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="38">
         <f>COUNTIF('Daily Log'!A5:A64,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+    <row r="9" ht="24" customHeight="1" spans="1:4">
+      <c r="A9" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Summary",'Unit Plan'!L5:L28,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="33" t="str">
+      <c r="D9" s="37" t="str">
         <f>IF(B6=B5,"All Completed","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" ht="24" customHeight="1" spans="1:4">
+      <c r="A10" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.90909090909090906</v>
-      </c>
-      <c r="C10" s="32" t="s">
+        <v>0.931818181818182</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="33" t="str">
+      <c r="D10" s="37" t="str">
         <f>IF(B6=0,"","See Unit Plan")</f>
         <v>See Unit Plan</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:4">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:4">
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:1">
+      <c r="A13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:4">
+      <c r="A15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(a)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.3(b)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.1–6.3")</f>
         <v>5</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+    <row r="16" ht="24" customHeight="1" spans="1:4">
+      <c r="A16" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="43">
         <f>COUNTIFS('Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="43">
         <f>COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.1")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.5.2")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 1)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.6 (part 2)")+COUNTIFS('Unit Plan'!Q5:Q28,"Completed",'Unit Plan'!D5:D28,"6.4–6.6")</f>
         <v>6</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="44" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:4">
+      <c r="A17" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="43">
         <f>COUNTIF('Unit Plan'!C5:C28,"Exercise")</f>
         <v>13</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="43">
         <f>COUNTIFS('Unit Plan'!C5:C28,"Exercise",'Unit Plan'!Q5:Q28,"Completed")</f>
         <v>13</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="44" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2110,15 +2647,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2130,17 +2668,10 @@
     <col min="10" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
       <c r="J1" t="s">
         <v>30</v>
       </c>
@@ -2148,7 +2679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="21.95" customHeight="1" spans="10:11">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -2156,17 +2687,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A3" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="33">
         <v>46114</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J3" t="s">
@@ -2176,7 +2707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="21.95" customHeight="1" spans="4:11">
       <c r="D4" t="s">
         <v>30</v>
       </c>
@@ -2187,17 +2718,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+    <row r="5" ht="21.95" customHeight="1" spans="1:11">
+      <c r="A5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
       <c r="J5" t="s">
         <v>41</v>
       </c>
@@ -2205,126 +2729,56 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+    <row r="6" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+    </row>
+    <row r="7" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A7" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-    </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+    </row>
+    <row r="8" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A8" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-    </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+    </row>
+    <row r="9" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-    </row>
-    <row r="10" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    </row>
+    <row r="10" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A10" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-    </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+    </row>
+    <row r="11" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A11" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-    </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+    </row>
+    <row r="12" ht="21.95" customHeight="1"/>
+    <row r="13" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A13" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-    </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+    </row>
+    <row r="14" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A14" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-    </row>
-    <row r="15" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+    </row>
+    <row r="15" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A15" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-    </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+    </row>
+    <row r="16" ht="21.95" customHeight="1" spans="1:1">
+      <c r="A16" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2333,32 +2787,33 @@
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="42" style="10" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
@@ -2374,2750 +2829,2720 @@
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="15.75"/>
+    <row r="4" ht="24" customHeight="1" spans="1:22">
+      <c r="A4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="S4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="24" customHeight="1" spans="1:22">
+      <c r="A5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <v>1</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G5-1)</f>
         <v>46114</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="19">
         <v>60</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="6" t="str">
+      <c r="J5" s="19"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="8" t="str">
         <f t="shared" ref="M5:M48" si="0">IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(L5-K5)*1440,"")</f>
         <v/>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="6" t="str">
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="8" t="str">
         <f t="shared" ref="P5:P48" si="1">IF(AND(N5&lt;&gt;"",O5&lt;&gt;""),(O5-N5)*1440,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="26" t="str">
+      <c r="R5" s="28" t="str">
         <f t="shared" ref="R5:R48" si="2">IF(O5&lt;&gt;"",INT(O5)+2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="25"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-    </row>
-    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="T5" s="27"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:22">
+      <c r="A6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="19">
         <v>2</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G6-1)</f>
         <v>46115</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="19">
         <v>60</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="6" t="str">
+      <c r="J6" s="19"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="6" t="str">
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R6" s="26" t="str">
+      <c r="R6" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="S6" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T6" s="25"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-    </row>
-    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="T6" s="27"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:22">
+      <c r="A7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="19">
         <v>3</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G7-1)</f>
         <v>46116</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="19">
         <v>75</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="6" t="str">
+      <c r="J7" s="19"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="6" t="str">
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="26" t="str">
+      <c r="R7" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T7" s="25"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-    </row>
-    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="T7" s="27"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:22">
+      <c r="A8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="19">
         <v>4</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G8-1)</f>
         <v>46117</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="19">
         <v>75</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="6" t="str">
+      <c r="J8" s="19"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="6" t="str">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="Q8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="26" t="str">
+      <c r="R8" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" s="25" t="s">
+      <c r="S8" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="25"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-    </row>
-    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="T8" s="27"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:22">
+      <c r="A9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="17">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="19">
         <v>5</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G9-1)</f>
         <v>46118</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17">
+      <c r="I9" s="19"/>
+      <c r="J9" s="19">
         <v>60</v>
       </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="6" t="str">
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N9" s="22">
-        <v>46118.416666666701</v>
-      </c>
-      <c r="O9" s="22">
+      <c r="N9" s="24">
+        <v>46118.4166666667</v>
+      </c>
+      <c r="O9" s="24">
         <v>46118.75</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="8">
         <f t="shared" si="1"/>
-        <v>479.99999995110556</v>
-      </c>
-      <c r="Q9" s="28" t="s">
+        <v>479.999999951106</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="28">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
-      <c r="S9" s="25" t="s">
+      <c r="S9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T9" s="28"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-    </row>
-    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="T9" s="30"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:22">
+      <c r="A10" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="17">
         <v>6</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="19">
         <v>6</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G10-1)</f>
         <v>46119</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17">
+      <c r="I10" s="19"/>
+      <c r="J10" s="19">
         <v>60</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="6" t="str">
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N10" s="22">
-        <v>46119.541666666701</v>
-      </c>
-      <c r="O10" s="22">
+      <c r="N10" s="24">
+        <v>46119.5416666667</v>
+      </c>
+      <c r="O10" s="24">
         <v>46119.625</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="8">
         <f t="shared" si="1"/>
-        <v>119.99999995110556</v>
-      </c>
-      <c r="Q10" s="28" t="s">
+        <v>119.999999951106</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="28">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
-      <c r="S10" s="25" t="s">
+      <c r="S10" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T10" s="28"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-    </row>
-    <row r="11" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="T10" s="30"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:22">
+      <c r="A11" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="17">
         <v>7</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="19">
         <v>7</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G11-1)</f>
         <v>46120</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17">
+      <c r="I11" s="19"/>
+      <c r="J11" s="19">
         <v>50</v>
       </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="6" t="str">
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="6" t="str">
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="28" t="s">
+      <c r="Q11" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="26" t="str">
+      <c r="R11" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" s="25" t="s">
+      <c r="S11" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-    </row>
-    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="T11" s="30"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:22">
+      <c r="A12" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="17">
         <v>8</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <v>8</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G12-1)</f>
         <v>46121</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17">
+      <c r="I12" s="19"/>
+      <c r="J12" s="19">
         <v>50</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="6" t="str">
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N12" s="22">
-        <v>46121.583333333299</v>
-      </c>
-      <c r="O12" s="22">
+      <c r="N12" s="24">
+        <v>46121.5833333333</v>
+      </c>
+      <c r="O12" s="24">
         <v>46121.75</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v>240.00000004889444</v>
-      </c>
-      <c r="Q12" s="28" t="s">
+        <v>240.000000048894</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="28">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
-      <c r="S12" s="25" t="s">
+      <c r="S12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T12" s="28"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-    </row>
-    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="T12" s="30"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:22">
+      <c r="A13" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="17">
         <v>9</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <v>9</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G13-1)</f>
         <v>46122</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17">
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
         <v>50</v>
       </c>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="6" t="str">
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="6" t="str">
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="28" t="s">
+      <c r="Q13" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R13" s="26" t="str">
+      <c r="R13" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" s="25" t="s">
+      <c r="S13" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T13" s="28"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-    </row>
-    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="T13" s="30"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:22">
+      <c r="A14" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="17">
         <v>10</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="19">
         <v>10</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G14-1)</f>
         <v>46123</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17">
+      <c r="I14" s="19"/>
+      <c r="J14" s="19">
         <v>60</v>
       </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="6" t="str">
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="24">
         <v>46123</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="24">
         <v>46123</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q14" s="28" t="s">
+      <c r="Q14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="28">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
-      <c r="S14" s="25" t="s">
+      <c r="S14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T14" s="28"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-    </row>
-    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="T14" s="30"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:22">
+      <c r="A15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="17">
         <v>11</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <v>11</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G15-1)</f>
         <v>46124</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17">
+      <c r="I15" s="19"/>
+      <c r="J15" s="19">
         <v>60</v>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="6" t="str">
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="24">
         <v>46124</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="24">
         <v>46126</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="8">
         <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="Q15" s="28" t="s">
+      <c r="Q15" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="28">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
-      <c r="S15" s="25" t="s">
+      <c r="S15" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-    </row>
-    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="T15" s="30"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:22">
+      <c r="A16" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="21">
         <v>12</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="23">
         <v>12</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G16-1)</f>
         <v>46125</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="23">
         <v>45</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="6" t="str">
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="23" t="str">
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R16" s="26" t="str">
+      <c r="R16" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" s="29" t="s">
+      <c r="S16" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T16" s="29"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-    </row>
-    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:22">
+      <c r="A17" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="17">
         <v>13</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="19">
         <v>13</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G17-1)</f>
         <v>46126</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="19">
         <v>50</v>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="6" t="str">
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="6" t="str">
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R17" s="26" t="str">
+      <c r="R17" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" s="25" t="s">
+      <c r="S17" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T17" s="25"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-    </row>
-    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="T17" s="27"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:22">
+      <c r="A18" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <v>14</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="19">
         <v>14</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G18-1)</f>
         <v>46127</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="19">
         <v>70</v>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="6" t="str">
+      <c r="J18" s="19"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="6" t="str">
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="25" t="s">
+      <c r="Q18" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="26" t="str">
+      <c r="R18" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" s="25" t="s">
+      <c r="S18" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T18" s="25"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-    </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="T18" s="27"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:22">
+      <c r="A19" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="17">
         <v>15</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="19">
         <v>15</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G19-1)</f>
         <v>46128</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="19">
         <v>80</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="6" t="str">
+      <c r="J19" s="19"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="6" t="str">
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="25" t="s">
+      <c r="Q19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="26" t="str">
+      <c r="R19" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" s="25" t="s">
+      <c r="S19" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T19" s="25"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-    </row>
-    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="T19" s="27"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:22">
+      <c r="A20" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="17">
         <v>16</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="19">
         <v>16</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G20-1)</f>
         <v>46129</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="19">
         <v>60</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="6" t="str">
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="6" t="str">
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="26" t="str">
+      <c r="R20" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" s="25" t="s">
+      <c r="S20" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T20" s="25"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-    </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="T20" s="27"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:22">
+      <c r="A21" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="17">
         <v>17</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="19">
         <v>17</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G21-1)</f>
         <v>46130</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="19">
         <v>80</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="6" t="str">
+      <c r="J21" s="19"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="6" t="str">
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" s="25" t="s">
+      <c r="Q21" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="26" t="str">
+      <c r="R21" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" s="25" t="s">
+      <c r="S21" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T21" s="25"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-    </row>
-    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="T21" s="27"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:22">
+      <c r="A22" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="17">
         <v>18</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="19">
         <v>18</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G22-1)</f>
         <v>46131</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="19">
         <v>80</v>
       </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="6" t="str">
+      <c r="J22" s="19"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="6" t="str">
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" s="25" t="s">
+      <c r="Q22" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="26" t="str">
+      <c r="R22" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" s="25" t="s">
+      <c r="S22" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-    </row>
-    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="T22" s="27"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:22">
+      <c r="A23" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="17">
         <v>19</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="19">
         <v>19</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G23-1)</f>
         <v>46132</v>
       </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19">
         <v>60</v>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="6" t="str">
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="24">
         <v>46143</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="24">
         <v>46143</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="28" t="s">
+      <c r="Q23" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="28">
         <f t="shared" si="2"/>
         <v>46145</v>
       </c>
-      <c r="S23" s="25" t="s">
+      <c r="S23" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T23" s="28"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-    </row>
-    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="T23" s="30"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:22">
+      <c r="A24" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="17">
         <v>20</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="19">
         <v>20</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G24-1)</f>
         <v>46133</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19">
         <v>60</v>
       </c>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="6" t="str">
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="24">
         <v>46144</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="24">
         <v>46144</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="28" t="s">
+      <c r="Q24" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="28">
         <f t="shared" si="2"/>
         <v>46146</v>
       </c>
-      <c r="S24" s="25" t="s">
+      <c r="S24" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T24" s="28"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-    </row>
-    <row r="25" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="T24" s="30"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:22">
+      <c r="A25" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="17">
         <v>21</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <v>21</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G25-1)</f>
         <v>46134</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17">
+      <c r="I25" s="19"/>
+      <c r="J25" s="19">
         <v>60</v>
       </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="6" t="str">
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="24">
         <v>46145</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="24">
         <v>46145</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="28" t="s">
+      <c r="Q25" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="28">
         <f t="shared" si="2"/>
         <v>46147</v>
       </c>
-      <c r="S25" s="25" t="s">
+      <c r="S25" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T25" s="28"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-    </row>
-    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="T25" s="30"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:22">
+      <c r="A26" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <v>22</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="19">
         <v>22</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G26-1)</f>
         <v>46135</v>
       </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17">
+      <c r="I26" s="19"/>
+      <c r="J26" s="19">
         <v>60</v>
       </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="6" t="str">
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N26" s="22">
+      <c r="N26" s="24">
         <v>46147</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="24">
         <v>46147</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="28" t="s">
+      <c r="Q26" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="28">
         <f t="shared" si="2"/>
         <v>46149</v>
       </c>
-      <c r="S26" s="25" t="s">
+      <c r="S26" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T26" s="28"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-    </row>
-    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="T26" s="30"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:22">
+      <c r="A27" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="17">
         <v>23</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="19">
         <v>23</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G27-1)</f>
         <v>46136</v>
       </c>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17">
+      <c r="I27" s="19"/>
+      <c r="J27" s="19">
         <v>60</v>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="6" t="str">
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="24">
         <v>46148</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="24">
         <v>46148</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="28" t="s">
+      <c r="Q27" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="28">
         <f t="shared" si="2"/>
         <v>46150</v>
       </c>
-      <c r="S27" s="25" t="s">
+      <c r="S27" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T27" s="28"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-    </row>
-    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="T27" s="30"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:22">
+      <c r="A28" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="17">
         <v>24</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="19">
         <v>24</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G28-1)</f>
         <v>46137</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17">
+      <c r="I28" s="19"/>
+      <c r="J28" s="19">
         <v>70</v>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="6" t="str">
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N28" s="22">
+      <c r="N28" s="24">
         <v>46149</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="24">
         <v>46149</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="28" t="s">
+      <c r="Q28" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="28">
         <f t="shared" si="2"/>
         <v>46151</v>
       </c>
-      <c r="S28" s="25" t="s">
+      <c r="S28" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T28" s="28"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-    </row>
-    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="T28" s="30"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:22">
+      <c r="A29" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="17">
         <v>25</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="19">
         <v>25</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G29-1)</f>
         <v>46138</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17">
+      <c r="I29" s="19"/>
+      <c r="J29" s="19">
         <v>70</v>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="6" t="str">
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N29" s="22">
+      <c r="N29" s="24">
         <v>46150</v>
       </c>
-      <c r="O29" s="22">
+      <c r="O29" s="24">
         <v>46150</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="28" t="s">
+      <c r="Q29" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="28">
         <f t="shared" si="2"/>
         <v>46152</v>
       </c>
-      <c r="S29" s="25" t="s">
+      <c r="S29" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T29" s="28"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-    </row>
-    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="T29" s="30"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:22">
+      <c r="A30" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="17">
         <v>26</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="19">
         <v>26</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G30-1)</f>
         <v>46139</v>
       </c>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17">
+      <c r="I30" s="19"/>
+      <c r="J30" s="19">
         <v>70</v>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="6" t="str">
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N30" s="22">
+      <c r="N30" s="24">
         <v>46151</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="24">
         <v>46151</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="28" t="s">
+      <c r="Q30" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="28">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S30" s="25" t="s">
+      <c r="S30" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T30" s="28"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-    </row>
-    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="T30" s="30"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:22">
+      <c r="A31" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="17">
         <v>27</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="19">
         <v>27</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G31-1)</f>
         <v>46140</v>
       </c>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17">
+      <c r="I31" s="19"/>
+      <c r="J31" s="19">
         <v>70</v>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="6" t="str">
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="24">
         <v>46151</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="24">
         <v>46151</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="28" t="s">
+      <c r="Q31" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="28">
         <f t="shared" si="2"/>
         <v>46153</v>
       </c>
-      <c r="S31" s="25" t="s">
+      <c r="S31" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T31" s="28"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-    </row>
-    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="T31" s="30"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:22">
+      <c r="A32" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="17">
         <v>28</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="19">
         <v>28</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G32-1)</f>
         <v>46141</v>
       </c>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17">
+      <c r="I32" s="19"/>
+      <c r="J32" s="19">
         <v>70</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="6" t="str">
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N32" s="22">
+      <c r="N32" s="24">
         <v>46152</v>
       </c>
-      <c r="O32" s="22">
+      <c r="O32" s="24">
         <v>46152</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="28" t="s">
+      <c r="Q32" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="28">
         <f t="shared" si="2"/>
         <v>46154</v>
       </c>
-      <c r="S32" s="25" t="s">
+      <c r="S32" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T32" s="28"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-    </row>
-    <row r="33" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="T32" s="30"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:22">
+      <c r="A33" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="17">
         <v>29</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="19">
         <v>29</v>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G33-1)</f>
         <v>46142</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17">
+      <c r="I33" s="19"/>
+      <c r="J33" s="19">
         <v>70</v>
       </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="6" t="str">
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N33" s="22">
+      <c r="N33" s="24">
         <v>46153</v>
       </c>
-      <c r="O33" s="22">
+      <c r="O33" s="24">
         <v>46153</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="28" t="s">
+      <c r="Q33" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="28">
         <f t="shared" si="2"/>
         <v>46155</v>
       </c>
-      <c r="S33" s="25" t="s">
+      <c r="S33" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T33" s="28"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
-    </row>
-    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="T33" s="30"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:22">
+      <c r="A34" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="17">
         <v>30</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="19">
         <v>30</v>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G34-1)</f>
         <v>46143</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17">
+      <c r="I34" s="19"/>
+      <c r="J34" s="19">
         <v>70</v>
       </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="6" t="str">
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N34" s="22">
+      <c r="N34" s="24">
         <v>46154</v>
       </c>
-      <c r="O34" s="22">
+      <c r="O34" s="24">
         <v>46154</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="28" t="s">
+      <c r="Q34" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S34" s="25" t="s">
+      <c r="S34" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T34" s="28"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-    </row>
-    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="T34" s="30"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:22">
+      <c r="A35" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="17">
         <v>31</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="19">
         <v>31</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G35-1)</f>
         <v>46144</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17">
+      <c r="I35" s="19"/>
+      <c r="J35" s="19">
         <v>70</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="6" t="str">
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="24">
         <v>46154</v>
       </c>
-      <c r="O35" s="22">
+      <c r="O35" s="24">
         <v>46154</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="28" t="s">
+      <c r="Q35" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S35" s="25" t="s">
+      <c r="S35" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T35" s="28"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-    </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="T35" s="30"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:22">
+      <c r="A36" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="17">
         <v>32</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="19">
         <v>32</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G36-1)</f>
         <v>46145</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17">
+      <c r="I36" s="19"/>
+      <c r="J36" s="19">
         <v>70</v>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="6" t="str">
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N36" s="22">
+      <c r="N36" s="24">
         <v>46154</v>
       </c>
-      <c r="O36" s="22">
+      <c r="O36" s="24">
         <v>46154</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="28" t="s">
+      <c r="Q36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="28">
         <f t="shared" si="2"/>
         <v>46156</v>
       </c>
-      <c r="S36" s="25" t="s">
+      <c r="S36" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T36" s="28"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-    </row>
-    <row r="37" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="T36" s="30"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:22">
+      <c r="A37" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="17">
         <v>33</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="19">
         <v>33</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G37-1)</f>
         <v>46146</v>
       </c>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17">
+      <c r="I37" s="19"/>
+      <c r="J37" s="19">
         <v>70</v>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="6" t="str">
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="24">
         <v>46159</v>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="24">
         <v>46159</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="28" t="s">
+      <c r="Q37" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="28">
         <f t="shared" si="2"/>
         <v>46161</v>
       </c>
-      <c r="S37" s="25" t="s">
+      <c r="S37" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T37" s="28"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-    </row>
-    <row r="38" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="T37" s="30"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:22">
+      <c r="A38" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="17">
         <v>34</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="19">
         <v>34</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G38-1)</f>
         <v>46147</v>
       </c>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17">
+      <c r="I38" s="19"/>
+      <c r="J38" s="19">
         <v>70</v>
       </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="6" t="str">
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N38" s="22">
+      <c r="N38" s="24">
         <v>46160</v>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="24">
         <v>46160</v>
       </c>
-      <c r="P38" s="6">
+      <c r="P38" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="28" t="s">
+      <c r="Q38" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R38" s="26">
+      <c r="R38" s="28">
         <f t="shared" si="2"/>
         <v>46162</v>
       </c>
-      <c r="S38" s="25" t="s">
+      <c r="S38" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T38" s="28"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-    </row>
-    <row r="39" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="T38" s="30"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:22">
+      <c r="A39" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="17">
         <v>35</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="19">
         <v>35</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G39-1)</f>
         <v>46148</v>
       </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17">
+      <c r="I39" s="19"/>
+      <c r="J39" s="19">
         <v>70</v>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="6" t="str">
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N39" s="22">
+      <c r="N39" s="24">
         <v>46161</v>
       </c>
-      <c r="O39" s="22">
+      <c r="O39" s="24">
         <v>46161</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="28" t="s">
+      <c r="Q39" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R39" s="26">
+      <c r="R39" s="28">
         <f t="shared" si="2"/>
         <v>46163</v>
       </c>
-      <c r="S39" s="25" t="s">
+      <c r="S39" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T39" s="28"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
-    </row>
-    <row r="40" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="T39" s="30"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:22">
+      <c r="A40" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="17">
         <v>36</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="19">
         <v>36</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G40-1)</f>
         <v>46149</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17">
+      <c r="I40" s="19"/>
+      <c r="J40" s="19">
         <v>80</v>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="6" t="str">
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N40" s="22">
+      <c r="N40" s="24">
         <v>46162</v>
       </c>
-      <c r="O40" s="22">
+      <c r="O40" s="24">
         <v>46162</v>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="28" t="s">
+      <c r="Q40" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R40" s="26">
+      <c r="R40" s="28">
         <f t="shared" si="2"/>
         <v>46164</v>
       </c>
-      <c r="S40" s="25" t="s">
+      <c r="S40" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T40" s="28"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-    </row>
-    <row r="41" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="T40" s="30"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:22">
+      <c r="A41" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="17">
         <v>37</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="19">
         <v>37</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G41-1)</f>
         <v>46150</v>
       </c>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17">
+      <c r="I41" s="19"/>
+      <c r="J41" s="19">
         <v>80</v>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="6" t="str">
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="24">
         <v>46163</v>
       </c>
-      <c r="O41" s="22">
+      <c r="O41" s="24">
         <v>46163</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="28" t="s">
+      <c r="Q41" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R41" s="26">
+      <c r="R41" s="28">
         <f t="shared" si="2"/>
         <v>46165</v>
       </c>
-      <c r="S41" s="25" t="s">
+      <c r="S41" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T41" s="28"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-    </row>
-    <row r="42" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="T41" s="30"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:22">
+      <c r="A42" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="17">
         <v>38</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="19">
         <v>38</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G42-1)</f>
         <v>46151</v>
       </c>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17">
+      <c r="I42" s="19"/>
+      <c r="J42" s="19">
         <v>80</v>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="6" t="str">
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N42" s="22">
+      <c r="N42" s="24">
         <v>46164</v>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="24">
         <v>46164</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="28" t="s">
+      <c r="Q42" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R42" s="26">
+      <c r="R42" s="28">
         <f t="shared" si="2"/>
         <v>46166</v>
       </c>
-      <c r="S42" s="25" t="s">
+      <c r="S42" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T42" s="28"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-    </row>
-    <row r="43" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="T42" s="30"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:22">
+      <c r="A43" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="17">
         <v>39</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="19">
         <v>39</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G43-1)</f>
         <v>46152</v>
       </c>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17">
+      <c r="I43" s="19"/>
+      <c r="J43" s="19">
         <v>80</v>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="6" t="str">
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N43" s="22">
+      <c r="N43" s="24">
         <v>46165</v>
       </c>
-      <c r="O43" s="22">
+      <c r="O43" s="24">
         <v>46165</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="28" t="s">
+      <c r="Q43" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R43" s="26">
+      <c r="R43" s="28">
         <f t="shared" si="2"/>
         <v>46167</v>
       </c>
-      <c r="S43" s="25" t="s">
+      <c r="S43" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T43" s="28"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-    </row>
-    <row r="44" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="T43" s="30"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:22">
+      <c r="A44" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="17">
         <v>40</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="19">
         <v>40</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G44-1)</f>
         <v>46153</v>
       </c>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17">
+      <c r="I44" s="19"/>
+      <c r="J44" s="19">
         <v>80</v>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="6" t="str">
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="24">
         <v>46167</v>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="24">
         <v>46167</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="28" t="s">
+      <c r="Q44" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="R44" s="26">
+      <c r="R44" s="28">
         <f t="shared" si="2"/>
         <v>46169</v>
       </c>
-      <c r="S44" s="25" t="s">
+      <c r="S44" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T44" s="28"/>
-      <c r="U44" s="27"/>
-      <c r="V44" s="27"/>
-    </row>
-    <row r="45" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="T44" s="30"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:22">
+      <c r="A45" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="17">
         <v>41</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="F45" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="19">
         <v>41</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G45-1)</f>
         <v>46154</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17">
+      <c r="I45" s="19"/>
+      <c r="J45" s="19">
         <v>80</v>
       </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="6" t="str">
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="6" t="str">
+      <c r="N45" s="24">
+        <v>46168</v>
+      </c>
+      <c r="O45" s="24">
+        <v>46168</v>
+      </c>
+      <c r="P45" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q45" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R45" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" s="28">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S45" s="25" t="s">
+        <v>46170</v>
+      </c>
+      <c r="S45" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T45" s="28"/>
-      <c r="U45" s="27"/>
-      <c r="V45" s="27"/>
-    </row>
-    <row r="46" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="T45" s="30"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:22">
+      <c r="A46" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="17">
         <v>42</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="19">
         <v>42</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G46-1)</f>
         <v>46155</v>
       </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17">
+      <c r="I46" s="19"/>
+      <c r="J46" s="19">
         <v>70</v>
       </c>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="6" t="str">
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="6" t="str">
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q46" s="28" t="s">
+      <c r="Q46" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R46" s="26" t="str">
+      <c r="R46" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S46" s="25" t="s">
+      <c r="S46" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T46" s="28"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-    </row>
-    <row r="47" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="T46" s="30"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:22">
+      <c r="A47" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="17">
         <v>43</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="19">
         <v>43</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G47-1)</f>
         <v>46156</v>
       </c>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17">
+      <c r="I47" s="19"/>
+      <c r="J47" s="19">
         <v>70</v>
       </c>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="6" t="str">
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="6" t="str">
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q47" s="28" t="s">
+      <c r="Q47" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="R47" s="26" t="str">
+      <c r="R47" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S47" s="25" t="s">
+      <c r="S47" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="T47" s="28"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-    </row>
-    <row r="48" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="T47" s="30"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:22">
+      <c r="A48" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="21">
         <v>44</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="23">
         <v>44</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="20">
         <f>IF(Protocol!$B$3="","",Protocol!$B$3+G48-1)</f>
         <v>46157</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="23">
         <v>50</v>
       </c>
-      <c r="J48" s="21"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="6" t="str">
+      <c r="J48" s="23"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="23" t="str">
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q48" s="25" t="s">
+      <c r="Q48" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="R48" s="26" t="str">
+      <c r="R48" s="28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S48" s="29" t="s">
+      <c r="S48" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T48" s="29"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="E2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="Q5:Q28">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Completed">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="between" text="Completed">
       <formula>NOT(ISERROR(SEARCH("Completed",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Reading">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="between" text="Reading">
       <formula>NOT(ISERROR(SEARCH("Reading",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Doing Exercises">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="between" text="Doing Exercises">
       <formula>NOT(ISERROR(SEARCH("Doing Exercises",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Review Due">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="between" text="Review Due">
       <formula>NOT(ISERROR(SEARCH("Review Due",Q5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="between" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",Q5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48" xr:uid="{00000000-0002-0000-0200-000001000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
+      <formula1>Protocol!$J$1:$J$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
       <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
+      <formula1>Protocol!$K$1:$K$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$J$1:$J$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q5:Q48</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
-          <x14:formula1>
-            <xm:f>Protocol!$K$1:$K$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>T5:T48</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5128,778 +5553,772 @@
     <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" ht="30" spans="1:7">
+      <c r="A4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" ht="30" spans="1:7">
+      <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" ht="30" spans="1:7">
+      <c r="A6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" ht="30" spans="1:7">
+      <c r="A7" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" ht="30" spans="1:7">
+      <c r="A8" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="9">
         <v>21</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" ht="30" spans="1:7">
+      <c r="A9" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="9">
         <v>24</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" ht="30" spans="1:7">
+      <c r="A10" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>25</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" ht="30" spans="1:7">
+      <c r="A11" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <v>2</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" ht="30" spans="1:7">
+      <c r="A12" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="9">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" ht="30" spans="1:7">
+      <c r="A13" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="9">
         <v>5</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" ht="30" spans="1:7">
+      <c r="A14" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="9">
         <v>6</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" ht="30" spans="1:7">
+      <c r="A15" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="9">
         <v>8</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <v>3</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="9">
         <v>9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <v>10</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" ht="30" spans="1:7">
+      <c r="A19" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="9">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" ht="30" spans="1:7">
+      <c r="A20" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="30" spans="1:7">
+      <c r="A21" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="9">
         <v>18</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" ht="30" spans="1:7">
+      <c r="A22" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" ht="30" spans="1:7">
+      <c r="A23" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="9">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" ht="30" spans="1:7">
+      <c r="A24" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="9">
         <v>30</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" ht="30" spans="1:7">
+      <c r="A25" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="9">
         <v>11</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" ht="30" spans="1:7">
+      <c r="A26" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="9">
         <v>13</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" ht="30" spans="1:7">
+      <c r="A27" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="9">
         <v>14</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" ht="30" spans="1:7">
+      <c r="A28" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="9">
         <v>26</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" ht="30" spans="1:7">
+      <c r="A29" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="9">
         <v>27</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" ht="30" spans="1:7">
+      <c r="A30" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="9">
         <v>28</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" ht="30" spans="1:7">
+      <c r="A31" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="9">
         <v>23</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" ht="30" spans="1:7">
+      <c r="A32" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="9">
         <v>29</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" ht="30" spans="1:7">
+      <c r="A33" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="9">
         <v>33</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" ht="30" spans="1:7">
+      <c r="A34" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="9">
         <v>31</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" ht="30" spans="1:7">
+      <c r="A35" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="9">
         <v>32</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="11" t="s">
         <v>82</v>
       </c>
     </row>
@@ -5907,13 +6326,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G4:G35" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G4:G35">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5921,9 +6340,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -5935,1165 +6355,1147 @@
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" ht="19.5" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:10">
+      <c r="A5" s="4">
         <v>46114</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <f>IF(A5="","",A5-Protocol!$B$3+1)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6" t="str">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="str">
         <f t="shared" ref="F5:F36" si="0">IF(OR(D5&lt;&gt;"",E5&lt;&gt;""),SUM(D5:E5),"")</f>
         <v/>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4">
         <v>46115</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <f>IF(A6="","",A6-Protocol!$B$3+1)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6" t="str">
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4">
         <v>46118</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <f>IF(A7="","",A7-Protocol!$B$3+1)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6" t="str">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4">
         <v>46119</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <f>IF(A8="","",A8-Protocol!$B$3+1)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6" t="str">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4">
         <v>46120</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <f>IF(A9="","",A9-Protocol!$B$3+1)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6" t="str">
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4">
         <v>46121</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <f>IF(A10="","",A10-Protocol!$B$3+1)</f>
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6" t="str">
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="str">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="str">
         <f>IF(A11="","",A11-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="str">
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="str">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="str">
         <f>IF(A12="","",A12-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6" t="str">
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="str">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="str">
         <f>IF(A13="","",A13-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6" t="str">
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="str">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="str">
         <f>IF(A14="","",A14-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6" t="str">
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3" t="str">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="str">
         <f>IF(A15="","",A15-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="str">
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="str">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="str">
         <f>IF(A16="","",A16-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6" t="str">
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3" t="str">
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5" t="str">
         <f>IF(A17="","",A17-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6" t="str">
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="str">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="str">
         <f>IF(A18="","",A18-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6" t="str">
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="str">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5" t="str">
         <f>IF(A19="","",A19-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6" t="str">
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3" t="str">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="str">
         <f>IF(A20="","",A20-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6" t="str">
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3" t="str">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="str">
         <f>IF(A21="","",A21-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6" t="str">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3" t="str">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="str">
         <f>IF(A22="","",A22-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6" t="str">
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3" t="str">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="str">
         <f>IF(A23="","",A23-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6" t="str">
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3" t="str">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="str">
         <f>IF(A24="","",A24-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6" t="str">
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3" t="str">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="str">
         <f>IF(A25="","",A25-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6" t="str">
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="str">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="str">
         <f>IF(A26="","",A26-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6" t="str">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3" t="str">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5" t="str">
         <f>IF(A27="","",A27-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6" t="str">
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="str">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="str">
         <f>IF(A28="","",A28-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6" t="str">
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3" t="str">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5" t="str">
         <f>IF(A29="","",A29-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6" t="str">
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3" t="str">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="str">
         <f>IF(A30="","",A30-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6" t="str">
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3" t="str">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="str">
         <f>IF(A31="","",A31-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6" t="str">
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3" t="str">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="str">
         <f>IF(A32="","",A32-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6" t="str">
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3" t="str">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5" t="str">
         <f>IF(A33="","",A33-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="str">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3" t="str">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5" t="str">
         <f>IF(A34="","",A34-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6" t="str">
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3" t="str">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5" t="str">
         <f>IF(A35="","",A35-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6" t="str">
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3" t="str">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5" t="str">
         <f>IF(A36="","",A36-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6" t="str">
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3" t="str">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5" t="str">
         <f>IF(A37="","",A37-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6" t="str">
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8" t="str">
         <f t="shared" ref="F37:F64" si="1">IF(OR(D37&lt;&gt;"",E37&lt;&gt;""),SUM(D37:E37),"")</f>
         <v/>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3" t="str">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5" t="str">
         <f>IF(A38="","",A38-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6" t="str">
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3" t="str">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5" t="str">
         <f>IF(A39="","",A39-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6" t="str">
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3" t="str">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5" t="str">
         <f>IF(A40="","",A40-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6" t="str">
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3" t="str">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5" t="str">
         <f>IF(A41="","",A41-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6" t="str">
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3" t="str">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5" t="str">
         <f>IF(A42="","",A42-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6" t="str">
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3" t="str">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5" t="str">
         <f>IF(A43="","",A43-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6" t="str">
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3" t="str">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5" t="str">
         <f>IF(A44="","",A44-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6" t="str">
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3" t="str">
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5" t="str">
         <f>IF(A45="","",A45-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6" t="str">
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3" t="str">
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5" t="str">
         <f>IF(A46="","",A46-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6" t="str">
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3" t="str">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5" t="str">
         <f>IF(A47="","",A47-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6" t="str">
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3" t="str">
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5" t="str">
         <f>IF(A48="","",A48-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6" t="str">
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3" t="str">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5" t="str">
         <f>IF(A49="","",A49-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6" t="str">
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3" t="str">
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5" t="str">
         <f>IF(A50="","",A50-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6" t="str">
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3" t="str">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5" t="str">
         <f>IF(A51="","",A51-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6" t="str">
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3" t="str">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5" t="str">
         <f>IF(A52="","",A52-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6" t="str">
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3" t="str">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5" t="str">
         <f>IF(A53="","",A53-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6" t="str">
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3" t="str">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5" t="str">
         <f>IF(A54="","",A54-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6" t="str">
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3" t="str">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5" t="str">
         <f>IF(A55="","",A55-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6" t="str">
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="3" t="str">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5" t="str">
         <f>IF(A56="","",A56-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6" t="str">
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3" t="str">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5" t="str">
         <f>IF(A57="","",A57-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6" t="str">
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3" t="str">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5" t="str">
         <f>IF(A58="","",A58-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6" t="str">
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3" t="str">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5" t="str">
         <f>IF(A59="","",A59-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6" t="str">
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3" t="str">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5" t="str">
         <f>IF(A60="","",A60-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6" t="str">
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3" t="str">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5" t="str">
         <f>IF(A61="","",A61-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6" t="str">
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3" t="str">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5" t="str">
         <f>IF(A62="","",A62-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6" t="str">
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3" t="str">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5" t="str">
         <f>IF(A63="","",A63-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6" t="str">
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3" t="str">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5" t="str">
         <f>IF(A64="","",A64-Protocol!$B$3+1)</f>
         <v/>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="6" t="str">
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -894,15 +894,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,13 +950,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -968,39 +961,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1015,7 +984,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1023,6 +992,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1053,21 +1030,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1089,24 +1097,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1176,7 +1169,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1188,7 +1199,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1200,7 +1259,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1218,13 +1277,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1242,121 +1343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1390,41 +1383,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1446,9 +1409,50 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1476,27 +1480,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1505,136 +1498,136 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1643,7 +1636,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1658,10 +1651,10 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1670,7 +1663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1678,58 +1671,58 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1741,19 +1734,19 @@
     <xf numFmtId="178" fontId="6" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2464,7 +2457,7 @@
       </c>
       <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4">
@@ -2489,7 +2482,7 @@
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>9</v>
@@ -2512,7 +2505,7 @@
       </c>
       <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>132.857142855397</v>
+        <v>177.931034481073</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4">
@@ -2521,7 +2514,7 @@
       </c>
       <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>13</v>
@@ -2553,7 +2546,7 @@
       </c>
       <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.931818181818182</v>
+        <v>0.954545454545455</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>17</v>
@@ -5363,18 +5356,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="8" t="str">
+      <c r="N46" s="24">
+        <v>46169</v>
+      </c>
+      <c r="O46" s="24">
+        <v>46170</v>
+      </c>
+      <c r="P46" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1440</v>
       </c>
       <c r="Q46" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R46" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R46" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46172</v>
       </c>
       <c r="S46" s="27" t="s">
         <v>82</v>
@@ -5521,11 +5518,11 @@
     <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
       <formula1>Protocol!$J$1:$J$5</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
+      <formula1>Protocol!$K$1:$K$5</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="S5:S48">
       <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T5:T48">
-      <formula1>Protocol!$K$1:$K$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
+++ b/Chapter6_Study_Checkin_Record_English_One_Exercise_Per_Day.xlsx
@@ -894,11 +894,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
@@ -968,18 +968,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -990,8 +990,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -999,7 +1000,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1030,9 +1031,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1044,36 +1053,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -1097,9 +1076,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1169,7 +1169,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1181,7 +1223,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1193,13 +1235,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1211,37 +1265,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1259,61 +1307,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1331,25 +1325,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1392,52 +1392,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1460,23 +1425,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1486,10 +1486,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1498,133 +1498,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D4" s="38">
         <f>COUNTIFS('Unit Plan'!R5:R48,"&gt;0",'Unit Plan'!S5:S48,"&lt;&gt;Yes")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Unit Plan'!Q5:Q48,"Completed")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>9</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="D7" s="38">
         <f>IFERROR(AVERAGE('Unit Plan'!P5:P48),"")</f>
-        <v>177.931034481073</v>
+        <v>171.99999999837</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B8" s="38">
         <f>COUNTIFS('Unit Plan'!C5:C48,"Exercise",'Unit Plan'!O5:O48,"&lt;&gt;")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>13</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B10" s="39">
         <f>IF(B5=0,"",B6/B5)</f>
-        <v>0.954545454545455</v>
+        <v>0.977272727272727</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>17</v>
@@ -5416,18 +5416,22 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="8" t="str">
+      <c r="N47" s="24">
+        <v>46171</v>
+      </c>
+      <c r="O47" s="24">
+        <v>46171</v>
+      </c>
+      <c r="P47" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q47" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="R47" s="28" t="str">
+        <v>21</v>
+      </c>
+      <c r="R47" s="28">
         <f t="shared" si="2"/>
-        <v/>
+        <v>46173</v>
       </c>
       <c r="S47" s="27" t="s">
         <v>82</v>
@@ -5518,11 +5522,11 @@
     <dataValidation type="list" allowBlank="1" sqref="Q5:Q48">
       <formula1>Protocol!$J$1:$J$5</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="T5:T48">
       <formula1>Protocol!$K$1:$K$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S5:S48">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
